--- a/model/Outputs/11. Interest rate/0/Output Files/0.2/Output_9_48.xlsx
+++ b/model/Outputs/11. Interest rate/0/Output Files/0.2/Output_9_48.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4469230.0388327</v>
+        <v>4505604.686942449</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13279501.51514058</v>
+        <v>13275569.19337385</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13279501.51514058</v>
+        <v>13275569.19337385</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>987.0883260129722</v>
+        <v>603.5370117061212</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>987.0883260129722</v>
+        <v>603.5370117061212</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>19681618.32251783</v>
+        <v>19682406.75599255</v>
       </c>
     </row>
   </sheetData>
@@ -669,13 +669,13 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G2" t="n">
-        <v>1.415908396047419</v>
+        <v>3.34732203575993</v>
       </c>
       <c r="H2" t="n">
-        <v>3.769060713577687</v>
+        <v>3.81023156784903</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1.79868786782652</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -702,16 +702,16 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.575699570821598e-12</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>85.41253966161941</v>
+        <v>85.50414770182039</v>
       </c>
       <c r="T2" t="n">
-        <v>184.8629887637397</v>
+        <v>184.8805867536895</v>
       </c>
       <c r="U2" t="n">
-        <v>249.1881709204699</v>
+        <v>249.1884925285102</v>
       </c>
       <c r="V2" t="n">
         <v>229.8510241668239</v>
@@ -733,10 +733,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>348.9870716648493</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -748,13 +748,13 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>325.517988705216</v>
+        <v>325.5201396486123</v>
       </c>
       <c r="H3" t="n">
-        <v>330.0284079411381</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>209.4985557026693</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -778,19 +778,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>145.073529241423</v>
       </c>
       <c r="R3" t="n">
-        <v>133.5184388018132</v>
+        <v>133.6519859716245</v>
       </c>
       <c r="S3" t="n">
-        <v>62.44885845517734</v>
+        <v>62.48881128536601</v>
       </c>
       <c r="T3" t="n">
-        <v>4.464774651476091</v>
+        <v>4.473444462796863</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1957842884886531</v>
+        <v>0.1959257979225981</v>
       </c>
       <c r="V3" t="n">
         <v>14.51066719152016</v>
@@ -802,7 +802,7 @@
         <v>19.86273944538755</v>
       </c>
       <c r="Y3" t="n">
-        <v>315.1190419072851</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -845,22 +845,22 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>91.51638189435317</v>
+        <v>91.79905402550071</v>
       </c>
       <c r="N4" t="n">
-        <v>142.7621408454554</v>
+        <v>143.0380916651276</v>
       </c>
       <c r="O4" t="n">
-        <v>214.1923837511461</v>
+        <v>214.4472689970478</v>
       </c>
       <c r="P4" t="n">
-        <v>264.9837661807364</v>
+        <v>265.2018645413922</v>
       </c>
       <c r="Q4" t="n">
-        <v>310.286266425598</v>
+        <v>310.437266425598</v>
       </c>
       <c r="R4" t="n">
-        <v>318.2506853582003</v>
+        <v>318.3317673254134</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -906,10 +906,10 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G5" t="n">
-        <v>3.343301935257443</v>
+        <v>3.34732203575993</v>
       </c>
       <c r="H5" t="n">
-        <v>3.769060713577687</v>
+        <v>5.608919435675552</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -942,13 +942,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>87.36594612241093</v>
+        <v>85.50414770182039</v>
       </c>
       <c r="T5" t="n">
-        <v>184.8629887637397</v>
+        <v>184.8805867536895</v>
       </c>
       <c r="U5" t="n">
-        <v>249.1881709204699</v>
+        <v>249.1884925285102</v>
       </c>
       <c r="V5" t="n">
         <v>229.8510241668239</v>
@@ -970,16 +970,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="C6" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -991,7 +991,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>209.5726123064429</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1018,16 +1018,16 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>133.5184388018132</v>
+        <v>133.6519859716245</v>
       </c>
       <c r="S6" t="n">
-        <v>62.44885845517734</v>
+        <v>62.48881128536601</v>
       </c>
       <c r="T6" t="n">
-        <v>4.464774651476091</v>
+        <v>4.473444462796863</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1957842884886531</v>
+        <v>0.1959257979225981</v>
       </c>
       <c r="V6" t="n">
         <v>14.51066719152016</v>
@@ -1036,10 +1036,10 @@
         <v>32.37314290982852</v>
       </c>
       <c r="X6" t="n">
-        <v>151.9999216514115</v>
+        <v>242.9707801393486</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
     </row>
     <row r="7">
@@ -1082,22 +1082,22 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>91.51638189435317</v>
+        <v>91.79905402550071</v>
       </c>
       <c r="N7" t="n">
-        <v>142.7621408454554</v>
+        <v>143.0380916651276</v>
       </c>
       <c r="O7" t="n">
-        <v>214.1923837511461</v>
+        <v>214.4472689970478</v>
       </c>
       <c r="P7" t="n">
-        <v>264.9837661807364</v>
+        <v>265.2018645413922</v>
       </c>
       <c r="Q7" t="n">
-        <v>310.286266425598</v>
+        <v>310.437266425598</v>
       </c>
       <c r="R7" t="n">
-        <v>318.2506853582003</v>
+        <v>318.3317673254134</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1131,7 +1131,7 @@
         <v>81.99931295557451</v>
       </c>
       <c r="C8" t="n">
-        <v>51.42798470378535</v>
+        <v>49.47457824299391</v>
       </c>
       <c r="D8" t="n">
         <v>10.33915573984979</v>
@@ -1143,13 +1143,13 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G8" t="n">
-        <v>3.343301935257443</v>
+        <v>3.34732203575993</v>
       </c>
       <c r="H8" t="n">
-        <v>3.769060713577687</v>
+        <v>3.81023156784903</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1.79868786782652</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1179,13 +1179,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>85.41253966161941</v>
+        <v>85.50414770182039</v>
       </c>
       <c r="T8" t="n">
-        <v>184.8629887637397</v>
+        <v>184.8805867536895</v>
       </c>
       <c r="U8" t="n">
-        <v>249.1881709204699</v>
+        <v>249.1884925285102</v>
       </c>
       <c r="V8" t="n">
         <v>229.8510241668239</v>
@@ -1210,16 +1210,16 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>153.6008523136666</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -1228,7 +1228,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>125.4272025471402</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1255,25 +1255,25 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>133.5184388018132</v>
+        <v>133.6519859716245</v>
       </c>
       <c r="S9" t="n">
-        <v>62.44885845517734</v>
+        <v>62.48881128536601</v>
       </c>
       <c r="T9" t="n">
-        <v>4.464774651476091</v>
+        <v>4.473444462796863</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1957842884886531</v>
+        <v>0.1959257979225981</v>
       </c>
       <c r="V9" t="n">
-        <v>14.51066719152016</v>
+        <v>374</v>
       </c>
       <c r="W9" t="n">
-        <v>32.37314290982852</v>
+        <v>374</v>
       </c>
       <c r="X9" t="n">
-        <v>19.86273944538755</v>
+        <v>374</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
@@ -1319,22 +1319,22 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>91.51638189435317</v>
+        <v>91.79905402550071</v>
       </c>
       <c r="N10" t="n">
-        <v>142.7621408454554</v>
+        <v>143.0380916651276</v>
       </c>
       <c r="O10" t="n">
-        <v>214.1923837511461</v>
+        <v>214.4472689970478</v>
       </c>
       <c r="P10" t="n">
-        <v>264.9837661807364</v>
+        <v>265.2018645413922</v>
       </c>
       <c r="Q10" t="n">
-        <v>310.286266425598</v>
+        <v>310.437266425598</v>
       </c>
       <c r="R10" t="n">
-        <v>318.2506853582003</v>
+        <v>318.3317673254134</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1386,7 +1386,7 @@
         <v>72.84688483418068</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>0.4605873653143577</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1413,7 +1413,7 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.4605873653139497</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>142.3350019731772</v>
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>237.1483725282994</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C12" t="n">
         <v>40.09991244551929</v>
@@ -1456,16 +1456,16 @@
         <v>21.67209722191262</v>
       </c>
       <c r="F12" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G12" t="n">
         <v>3.99961134672543</v>
       </c>
       <c r="H12" t="n">
-        <v>4.021973978873973</v>
+        <v>325.021973978874</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>191.6509141932353</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1501,7 +1501,7 @@
         <v>81.3753501231742</v>
       </c>
       <c r="U12" t="n">
-        <v>79.16168051490371</v>
+        <v>400.1616805149037</v>
       </c>
       <c r="V12" t="n">
         <v>93.51066719152016</v>
@@ -1510,10 +1510,10 @@
         <v>111.3731429098285</v>
       </c>
       <c r="X12" t="n">
-        <v>419.8627394453875</v>
+        <v>401.8036411341252</v>
       </c>
       <c r="Y12" t="n">
-        <v>399.3913927661343</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="13">
@@ -1553,7 +1553,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>9.483546242607703</v>
+        <v>10.32179209220538</v>
       </c>
       <c r="M13" t="n">
         <v>102.3923982877958</v>
@@ -1565,7 +1565,7 @@
         <v>231.765039488851</v>
       </c>
       <c r="P13" t="n">
-        <v>291.4220612627038</v>
+        <v>290.5838154131063</v>
       </c>
       <c r="Q13" t="n">
         <v>352.895266425598</v>
@@ -1620,7 +1620,7 @@
         <v>81.3744577141519</v>
       </c>
       <c r="H14" t="n">
-        <v>72.84688483418068</v>
+        <v>73.30747219949504</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1653,7 +1653,7 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>142.7955893384911</v>
+        <v>142.3350019731772</v>
       </c>
       <c r="T14" t="n">
         <v>259.6218731858503</v>
@@ -1687,7 +1687,7 @@
         <v>40.09991244551929</v>
       </c>
       <c r="D15" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E15" t="n">
         <v>342.6720972219126</v>
@@ -1696,7 +1696,7 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G15" t="n">
-        <v>324.9996113467254</v>
+        <v>177.5914272286982</v>
       </c>
       <c r="H15" t="n">
         <v>4.021973978873973</v>
@@ -1750,7 +1750,7 @@
         <v>98.86273944538755</v>
       </c>
       <c r="Y15" t="n">
-        <v>251.9832086481071</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="16">
@@ -1851,7 +1851,7 @@
         <v>83.36328960686865</v>
       </c>
       <c r="F17" t="n">
-        <v>83.88962870801186</v>
+        <v>84.35021607332619</v>
       </c>
       <c r="G17" t="n">
         <v>81.3744577141519</v>
@@ -1860,7 +1860,7 @@
         <v>72.84688483418068</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4605873653143577</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2158,16 +2158,16 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C21" t="n">
-        <v>40.09991244551929</v>
+        <v>213.6917283274922</v>
       </c>
       <c r="D21" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E21" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F21" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G21" t="n">
         <v>3.99961134672543</v>
@@ -2215,16 +2215,16 @@
         <v>79.16168051490371</v>
       </c>
       <c r="V21" t="n">
-        <v>414.5106671915202</v>
+        <v>93.51066719152016</v>
       </c>
       <c r="W21" t="n">
-        <v>432.3731429098285</v>
+        <v>111.3731429098285</v>
       </c>
       <c r="X21" t="n">
-        <v>419.8627394453875</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y21" t="n">
-        <v>251.9832086481073</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="22">
@@ -2264,7 +2264,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>10.32179209220538</v>
+        <v>9.483546242607703</v>
       </c>
       <c r="M22" t="n">
         <v>102.3923982877958</v>
@@ -2285,7 +2285,7 @@
         <v>377.7099312598395</v>
       </c>
       <c r="S22" t="n">
-        <v>29.72461090243831</v>
+        <v>30.56285675203577</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -2325,7 +2325,7 @@
         <v>83.36328960686865</v>
       </c>
       <c r="F23" t="n">
-        <v>84.350216073326</v>
+        <v>83.88962870801186</v>
       </c>
       <c r="G23" t="n">
         <v>81.37445771415189</v>
@@ -2334,7 +2334,7 @@
         <v>72.84688483418068</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>0.4605873653141466</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2392,10 +2392,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>63.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C24" t="n">
-        <v>40.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D24" t="n">
         <v>26.93768689770263</v>
@@ -2446,22 +2446,22 @@
         <v>131.8202263797056</v>
       </c>
       <c r="T24" t="n">
-        <v>254.9671660051473</v>
+        <v>81.3753501231742</v>
       </c>
       <c r="U24" t="n">
         <v>79.16168051490372</v>
       </c>
       <c r="V24" t="n">
-        <v>414.5106671915202</v>
+        <v>93.51066719152016</v>
       </c>
       <c r="W24" t="n">
-        <v>432.3731429098285</v>
+        <v>111.3731429098285</v>
       </c>
       <c r="X24" t="n">
-        <v>419.8627394453875</v>
+        <v>272.4545553273608</v>
       </c>
       <c r="Y24" t="n">
-        <v>78.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="25">
@@ -2565,13 +2565,13 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G26" t="n">
-        <v>81.3744577141519</v>
+        <v>81.37445771415189</v>
       </c>
       <c r="H26" t="n">
         <v>72.84688483418068</v>
       </c>
       <c r="I26" t="n">
-        <v>0.4605873653143577</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2598,7 +2598,7 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>0.4605873653139497</v>
       </c>
       <c r="S26" t="n">
         <v>142.3350019731772</v>
@@ -2629,7 +2629,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>63.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C27" t="n">
         <v>40.09991244551929</v>
@@ -2644,13 +2644,13 @@
         <v>18.63624233787687</v>
       </c>
       <c r="G27" t="n">
-        <v>3.99961134672543</v>
+        <v>3.999611346725456</v>
       </c>
       <c r="H27" t="n">
         <v>325.021973978874</v>
       </c>
       <c r="I27" t="n">
-        <v>191.6509141932353</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2680,25 +2680,25 @@
         <v>180.333570877285</v>
       </c>
       <c r="S27" t="n">
-        <v>131.8202263797057</v>
+        <v>131.8202263797056</v>
       </c>
       <c r="T27" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U27" t="n">
-        <v>79.16168051490371</v>
+        <v>252.7534963968768</v>
       </c>
       <c r="V27" t="n">
         <v>93.51066719152016</v>
       </c>
       <c r="W27" t="n">
-        <v>111.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X27" t="n">
-        <v>419.8627394453875</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y27" t="n">
-        <v>381.332294454872</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="28">
@@ -2750,13 +2750,13 @@
         <v>231.765039488851</v>
       </c>
       <c r="P28" t="n">
-        <v>291.4220612627038</v>
+        <v>291.4220612627037</v>
       </c>
       <c r="Q28" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R28" t="n">
-        <v>377.7099312598395</v>
+        <v>377.7099312598396</v>
       </c>
       <c r="S28" t="n">
         <v>30.56285675203577</v>
@@ -2799,16 +2799,16 @@
         <v>83.36328960686865</v>
       </c>
       <c r="F29" t="n">
-        <v>84.350216073326</v>
+        <v>83.88962870801186</v>
       </c>
       <c r="G29" t="n">
-        <v>81.37445771415189</v>
+        <v>81.3744577141519</v>
       </c>
       <c r="H29" t="n">
         <v>72.84688483418068</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>0.4605873653143577</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2878,13 +2878,13 @@
         <v>21.67209722191262</v>
       </c>
       <c r="F30" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G30" t="n">
-        <v>177.5914272286988</v>
+        <v>3.99961134672543</v>
       </c>
       <c r="H30" t="n">
-        <v>325.021973978874</v>
+        <v>4.021973978873973</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -2917,25 +2917,25 @@
         <v>180.333570877285</v>
       </c>
       <c r="S30" t="n">
-        <v>131.8202263797056</v>
+        <v>131.8202263797057</v>
       </c>
       <c r="T30" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U30" t="n">
-        <v>400.1616805149037</v>
+        <v>79.16168051490371</v>
       </c>
       <c r="V30" t="n">
-        <v>93.51066719152016</v>
+        <v>267.1024830734931</v>
       </c>
       <c r="W30" t="n">
-        <v>111.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X30" t="n">
-        <v>98.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y30" t="n">
-        <v>78.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="31">
@@ -2975,7 +2975,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>10.3217920922054</v>
+        <v>10.32179209220538</v>
       </c>
       <c r="M31" t="n">
         <v>102.3923982877958</v>
@@ -2984,16 +2984,16 @@
         <v>155.2579933044718</v>
       </c>
       <c r="O31" t="n">
-        <v>231.765039488851</v>
+        <v>230.9267936392535</v>
       </c>
       <c r="P31" t="n">
-        <v>291.4220612627037</v>
+        <v>291.4220612627038</v>
       </c>
       <c r="Q31" t="n">
-        <v>352.0570205760006</v>
+        <v>352.895266425598</v>
       </c>
       <c r="R31" t="n">
-        <v>377.7099312598396</v>
+        <v>377.7099312598395</v>
       </c>
       <c r="S31" t="n">
         <v>30.56285675203577</v>
@@ -3045,7 +3045,7 @@
         <v>72.84688483418068</v>
       </c>
       <c r="I32" t="n">
-        <v>0.4605873653141466</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3093,7 +3093,7 @@
         <v>271.2818334606677</v>
       </c>
       <c r="Y32" t="n">
-        <v>190.3174326828064</v>
+        <v>190.7780200481205</v>
       </c>
     </row>
     <row r="33">
@@ -3109,16 +3109,16 @@
         <v>40.09991244551929</v>
       </c>
       <c r="D33" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E33" t="n">
-        <v>342.6720972219126</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F33" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G33" t="n">
-        <v>3.999611346725456</v>
+        <v>177.5914272286987</v>
       </c>
       <c r="H33" t="n">
         <v>4.021973978873961</v>
@@ -3151,7 +3151,7 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>180.333570877285</v>
+        <v>501.333570877285</v>
       </c>
       <c r="S33" t="n">
         <v>131.8202263797056</v>
@@ -3166,10 +3166,10 @@
         <v>93.51066719152016</v>
       </c>
       <c r="W33" t="n">
-        <v>284.9649587918016</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X33" t="n">
-        <v>98.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y33" t="n">
         <v>78.39139276613435</v>
@@ -3276,13 +3276,13 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G35" t="n">
-        <v>81.3744577141519</v>
+        <v>81.37445771415189</v>
       </c>
       <c r="H35" t="n">
         <v>72.84688483418068</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>0.4605873653141466</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>0.4605873653139497</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>142.3350019731772</v>
@@ -3340,25 +3340,25 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>384.5565566463266</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C36" t="n">
-        <v>361.0999124455193</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D36" t="n">
         <v>26.93768689770263</v>
       </c>
       <c r="E36" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F36" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G36" t="n">
-        <v>3.99961134672543</v>
+        <v>177.5914272286987</v>
       </c>
       <c r="H36" t="n">
-        <v>4.021973978873973</v>
+        <v>4.021973978873961</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
@@ -3385,28 +3385,28 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
         <v>180.333570877285</v>
       </c>
       <c r="S36" t="n">
-        <v>131.8202263797057</v>
+        <v>131.8202263797056</v>
       </c>
       <c r="T36" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U36" t="n">
-        <v>79.16168051490371</v>
+        <v>79.16168051490372</v>
       </c>
       <c r="V36" t="n">
-        <v>414.5106671915202</v>
+        <v>93.51066719152016</v>
       </c>
       <c r="W36" t="n">
-        <v>206.3364106824544</v>
+        <v>111.3731429098285</v>
       </c>
       <c r="X36" t="n">
-        <v>98.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y36" t="n">
         <v>78.39139276613435</v>
@@ -3449,7 +3449,7 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>10.32179209220538</v>
+        <v>10.3217920922054</v>
       </c>
       <c r="M37" t="n">
         <v>102.3923982877958</v>
@@ -3461,16 +3461,16 @@
         <v>231.765039488851</v>
       </c>
       <c r="P37" t="n">
-        <v>291.4220612627038</v>
+        <v>291.4220612627037</v>
       </c>
       <c r="Q37" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R37" t="n">
-        <v>377.7099312598395</v>
+        <v>377.7099312598396</v>
       </c>
       <c r="S37" t="n">
-        <v>29.72461090243831</v>
+        <v>29.72461090246903</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -3513,7 +3513,7 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G38" t="n">
-        <v>81.37445771415189</v>
+        <v>81.3744577141519</v>
       </c>
       <c r="H38" t="n">
         <v>72.84688483418068</v>
@@ -3577,25 +3577,25 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>237.1483725282997</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C39" t="n">
-        <v>361.0999124455193</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D39" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E39" t="n">
-        <v>21.67209722191262</v>
+        <v>195.2639131038856</v>
       </c>
       <c r="F39" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G39" t="n">
-        <v>3.999611346725456</v>
+        <v>3.99961134672543</v>
       </c>
       <c r="H39" t="n">
-        <v>4.021973978873961</v>
+        <v>4.021973978873973</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -3628,13 +3628,13 @@
         <v>180.333570877285</v>
       </c>
       <c r="S39" t="n">
-        <v>131.8202263797056</v>
+        <v>131.8202263797057</v>
       </c>
       <c r="T39" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U39" t="n">
-        <v>79.16168051490372</v>
+        <v>79.16168051490371</v>
       </c>
       <c r="V39" t="n">
         <v>93.51066719152016</v>
@@ -3643,7 +3643,7 @@
         <v>111.3731429098285</v>
       </c>
       <c r="X39" t="n">
-        <v>98.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y39" t="n">
         <v>78.39139276613435</v>
@@ -3686,7 +3686,7 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>10.3217920922054</v>
+        <v>10.32179209220538</v>
       </c>
       <c r="M40" t="n">
         <v>102.3923982877958</v>
@@ -3698,16 +3698,16 @@
         <v>231.765039488851</v>
       </c>
       <c r="P40" t="n">
-        <v>291.4220612627037</v>
+        <v>291.4220612627038</v>
       </c>
       <c r="Q40" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R40" t="n">
-        <v>377.7099312598396</v>
+        <v>377.7099312598395</v>
       </c>
       <c r="S40" t="n">
-        <v>29.72461090243842</v>
+        <v>29.72461090247567</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -3756,7 +3756,7 @@
         <v>72.84688483418068</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>0.4605873653141466</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3783,7 +3783,7 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>0.4605873653139497</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>142.3350019731772</v>
@@ -3817,16 +3817,16 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C42" t="n">
-        <v>361.0999124455193</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D42" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E42" t="n">
         <v>21.67209722191262</v>
       </c>
       <c r="F42" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G42" t="n">
         <v>3.999611346725456</v>
@@ -3835,7 +3835,7 @@
         <v>4.021973978873961</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>173.5918158819733</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3862,13 +3862,13 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>353.9253867592579</v>
+        <v>501.333570877285</v>
       </c>
       <c r="S42" t="n">
-        <v>131.8202263797056</v>
+        <v>452.8202263797057</v>
       </c>
       <c r="T42" t="n">
-        <v>81.3753501231742</v>
+        <v>402.3753501231742</v>
       </c>
       <c r="U42" t="n">
         <v>79.16168051490372</v>
@@ -3926,7 +3926,7 @@
         <v>10.3217920922054</v>
       </c>
       <c r="M43" t="n">
-        <v>102.3923982877958</v>
+        <v>101.5541524381981</v>
       </c>
       <c r="N43" t="n">
         <v>155.2579933044718</v>
@@ -3944,7 +3944,7 @@
         <v>377.7099312598396</v>
       </c>
       <c r="S43" t="n">
-        <v>29.72461090243842</v>
+        <v>30.56285675203577</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -3987,13 +3987,13 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G44" t="n">
-        <v>81.3744577141519</v>
+        <v>81.37445771415189</v>
       </c>
       <c r="H44" t="n">
-        <v>72.84688483418068</v>
+        <v>73.30747219949482</v>
       </c>
       <c r="I44" t="n">
-        <v>0.4605873653143577</v>
+        <v>0</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4057,7 +4057,7 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D45" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E45" t="n">
         <v>21.67209722191262</v>
@@ -4066,13 +4066,13 @@
         <v>18.63624233787687</v>
       </c>
       <c r="G45" t="n">
-        <v>3.99961134672543</v>
+        <v>3.999611346725456</v>
       </c>
       <c r="H45" t="n">
-        <v>4.021973978873973</v>
+        <v>4.021973978873961</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>191.6509141932353</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4099,16 +4099,16 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>180.333570877285</v>
+        <v>483.2744725660229</v>
       </c>
       <c r="S45" t="n">
-        <v>131.8202263797057</v>
+        <v>131.8202263797056</v>
       </c>
       <c r="T45" t="n">
-        <v>254.9671660051471</v>
+        <v>81.3753501231742</v>
       </c>
       <c r="U45" t="n">
-        <v>79.16168051490371</v>
+        <v>79.16168051490372</v>
       </c>
       <c r="V45" t="n">
         <v>93.51066719152016</v>
@@ -4160,7 +4160,7 @@
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>10.32179209220538</v>
+        <v>10.3217920922054</v>
       </c>
       <c r="M46" t="n">
         <v>102.3923982877958</v>
@@ -4172,13 +4172,13 @@
         <v>231.765039488851</v>
       </c>
       <c r="P46" t="n">
-        <v>291.4220612627038</v>
+        <v>291.4220612627037</v>
       </c>
       <c r="Q46" t="n">
-        <v>352.0570205760006</v>
+        <v>352.895266425598</v>
       </c>
       <c r="R46" t="n">
-        <v>377.7099312598395</v>
+        <v>376.8716854102422</v>
       </c>
       <c r="S46" t="n">
         <v>30.56285675203577</v>
@@ -4297,76 +4297,76 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>104.8416377852013</v>
+        <v>108.731003807232</v>
       </c>
       <c r="C2" t="n">
-        <v>54.86731632763171</v>
+        <v>58.7566823496624</v>
       </c>
       <c r="D2" t="n">
-        <v>44.42372467121778</v>
+        <v>48.31309069324847</v>
       </c>
       <c r="E2" t="n">
-        <v>40.01636143195653</v>
+        <v>43.90572745398721</v>
       </c>
       <c r="F2" t="n">
-        <v>35.07734253497485</v>
+        <v>38.96670855700554</v>
       </c>
       <c r="G2" t="n">
-        <v>33.64713203391685</v>
+        <v>35.58557518755106</v>
       </c>
       <c r="H2" t="n">
-        <v>29.84</v>
+        <v>31.736856432148</v>
       </c>
       <c r="I2" t="n">
-        <v>29.84</v>
+        <v>29.92</v>
       </c>
       <c r="J2" t="n">
-        <v>29.93969029977264</v>
+        <v>400.18</v>
       </c>
       <c r="K2" t="n">
-        <v>82.08427879223495</v>
+        <v>770.4399999999999</v>
       </c>
       <c r="L2" t="n">
-        <v>146.7742517570591</v>
+        <v>1067.648108133742</v>
       </c>
       <c r="M2" t="n">
-        <v>516.0442517570591</v>
+        <v>1437.908108133742</v>
       </c>
       <c r="N2" t="n">
-        <v>885.3142517570591</v>
+        <v>1437.908108133742</v>
       </c>
       <c r="O2" t="n">
-        <v>1064.065793611129</v>
+        <v>1437.908108133742</v>
       </c>
       <c r="P2" t="n">
-        <v>1122.73</v>
+        <v>1496</v>
       </c>
       <c r="Q2" t="n">
-        <v>1492</v>
+        <v>1496</v>
       </c>
       <c r="R2" t="n">
-        <v>1491.999999999998</v>
+        <v>1496</v>
       </c>
       <c r="S2" t="n">
-        <v>1405.724707412504</v>
+        <v>1409.632174038565</v>
       </c>
       <c r="T2" t="n">
-        <v>1218.994415731959</v>
+        <v>1222.884106610596</v>
       </c>
       <c r="U2" t="n">
-        <v>967.2891925799692</v>
+        <v>971.1785586019998</v>
       </c>
       <c r="V2" t="n">
-        <v>735.1164408963086</v>
+        <v>739.0058069183393</v>
       </c>
       <c r="W2" t="n">
-        <v>494.3351520266646</v>
+        <v>498.2245180486953</v>
       </c>
       <c r="X2" t="n">
-        <v>300.1110778239699</v>
+        <v>304.0004438460006</v>
       </c>
       <c r="Y2" t="n">
-        <v>187.669226629216</v>
+        <v>191.5585926512467</v>
       </c>
     </row>
     <row r="3">
@@ -4376,76 +4376,76 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>903.6227801505288</v>
+        <v>726.6895778073549</v>
       </c>
       <c r="C3" t="n">
-        <v>903.6227801505288</v>
+        <v>361.9421914987495</v>
       </c>
       <c r="D3" t="n">
-        <v>903.6227801505288</v>
+        <v>361.9421914987495</v>
       </c>
       <c r="E3" t="n">
-        <v>903.6227801505288</v>
+        <v>361.9421914987495</v>
       </c>
       <c r="F3" t="n">
-        <v>903.6227801505288</v>
+        <v>361.9421914987495</v>
       </c>
       <c r="G3" t="n">
-        <v>574.8167309533409</v>
+        <v>33.13396963146437</v>
       </c>
       <c r="H3" t="n">
-        <v>241.454702729969</v>
+        <v>33.13396963146437</v>
       </c>
       <c r="I3" t="n">
-        <v>29.84</v>
+        <v>33.13396963146437</v>
       </c>
       <c r="J3" t="n">
-        <v>170.7984703728012</v>
+        <v>177.6113405614803</v>
       </c>
       <c r="K3" t="n">
-        <v>395.4085458068072</v>
+        <v>401.8775591086939</v>
       </c>
       <c r="L3" t="n">
-        <v>714.3818833454036</v>
+        <v>720.3885386284223</v>
       </c>
       <c r="M3" t="n">
-        <v>856.0360750882628</v>
+        <v>861.5031803712816</v>
       </c>
       <c r="N3" t="n">
-        <v>1046.360878846775</v>
+        <v>1051.274153846774</v>
       </c>
       <c r="O3" t="n">
-        <v>1337.587921002191</v>
+        <v>1341.994549492757</v>
       </c>
       <c r="P3" t="n">
-        <v>1492</v>
+        <v>1496</v>
       </c>
       <c r="Q3" t="n">
-        <v>1492</v>
+        <v>1349.46108157432</v>
       </c>
       <c r="R3" t="n">
-        <v>1357.132890099179</v>
+        <v>1214.459075542376</v>
       </c>
       <c r="S3" t="n">
-        <v>1294.053235093949</v>
+        <v>1151.339064143017</v>
       </c>
       <c r="T3" t="n">
-        <v>1289.54336170862</v>
+        <v>1146.820433372515</v>
       </c>
       <c r="U3" t="n">
-        <v>1289.345599801055</v>
+        <v>1146.622528526128</v>
       </c>
       <c r="V3" t="n">
-        <v>1274.688360213661</v>
+        <v>1131.965288938734</v>
       </c>
       <c r="W3" t="n">
-        <v>1241.988215860299</v>
+        <v>1099.265144585372</v>
       </c>
       <c r="X3" t="n">
-        <v>1221.92484268314</v>
+        <v>1079.201771408213</v>
       </c>
       <c r="Y3" t="n">
-        <v>903.6227801505288</v>
+        <v>1079.201771408213</v>
       </c>
     </row>
     <row r="4">
@@ -4455,76 +4455,76 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1016.117095409585</v>
+        <v>70.34367574991084</v>
       </c>
       <c r="C4" t="n">
-        <v>1016.117095409585</v>
+        <v>131.7094052417345</v>
       </c>
       <c r="D4" t="n">
-        <v>1016.117095409585</v>
+        <v>245.0285493667346</v>
       </c>
       <c r="E4" t="n">
-        <v>1016.117095409585</v>
+        <v>362.8574535781477</v>
       </c>
       <c r="F4" t="n">
-        <v>1016.117095409585</v>
+        <v>487.2184261700831</v>
       </c>
       <c r="G4" t="n">
-        <v>1016.117095409585</v>
+        <v>487.2184261700831</v>
       </c>
       <c r="H4" t="n">
-        <v>1016.117095409585</v>
+        <v>658.3540021491528</v>
       </c>
       <c r="I4" t="n">
-        <v>1016.117095409585</v>
+        <v>884.9629768229406</v>
       </c>
       <c r="J4" t="n">
-        <v>1385.387095409585</v>
+        <v>1255.222976822941</v>
       </c>
       <c r="K4" t="n">
-        <v>1385.387095409585</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="L4" t="n">
-        <v>1385.387095409585</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="M4" t="n">
-        <v>1292.946305617309</v>
+        <v>1294.017231267251</v>
       </c>
       <c r="N4" t="n">
-        <v>1148.742122945132</v>
+        <v>1149.534310393385</v>
       </c>
       <c r="O4" t="n">
-        <v>932.3861797621563</v>
+        <v>932.9209073660642</v>
       </c>
       <c r="P4" t="n">
-        <v>664.7258098826245</v>
+        <v>665.0402361121327</v>
       </c>
       <c r="Q4" t="n">
-        <v>351.3053387456568</v>
+        <v>351.4672397226398</v>
       </c>
       <c r="R4" t="n">
-        <v>29.84</v>
+        <v>29.92</v>
       </c>
       <c r="S4" t="n">
-        <v>29.84</v>
+        <v>70.34367574991084</v>
       </c>
       <c r="T4" t="n">
-        <v>218.7013496506081</v>
+        <v>70.34367574991084</v>
       </c>
       <c r="U4" t="n">
-        <v>465.2625721249603</v>
+        <v>70.34367574991084</v>
       </c>
       <c r="V4" t="n">
-        <v>664.0839650109062</v>
+        <v>70.34367574991084</v>
       </c>
       <c r="W4" t="n">
-        <v>835.9748832705836</v>
+        <v>70.34367574991084</v>
       </c>
       <c r="X4" t="n">
-        <v>987.0056742947771</v>
+        <v>70.34367574991084</v>
       </c>
       <c r="Y4" t="n">
-        <v>1016.117095409585</v>
+        <v>70.34367574991084</v>
       </c>
     </row>
     <row r="5">
@@ -4534,22 +4534,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>106.8684999460195</v>
+        <v>108.731003807232</v>
       </c>
       <c r="C5" t="n">
-        <v>56.89417848844992</v>
+        <v>58.7566823496624</v>
       </c>
       <c r="D5" t="n">
-        <v>46.450586832036</v>
+        <v>48.31309069324847</v>
       </c>
       <c r="E5" t="n">
-        <v>42.04322359277474</v>
+        <v>43.90572745398721</v>
       </c>
       <c r="F5" t="n">
-        <v>37.10420469579307</v>
+        <v>38.96670855700554</v>
       </c>
       <c r="G5" t="n">
-        <v>33.72713203391686</v>
+        <v>35.58557518755106</v>
       </c>
       <c r="H5" t="n">
         <v>29.92</v>
@@ -4558,25 +4558,25 @@
         <v>29.92</v>
       </c>
       <c r="J5" t="n">
-        <v>30.01969029977264</v>
+        <v>29.92</v>
       </c>
       <c r="K5" t="n">
-        <v>82.16427879223495</v>
+        <v>400.18</v>
       </c>
       <c r="L5" t="n">
-        <v>146.8542517570591</v>
+        <v>770.4399999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>146.8542517570591</v>
+        <v>770.4399999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>385.22</v>
+        <v>1140.7</v>
       </c>
       <c r="O5" t="n">
-        <v>755.48</v>
+        <v>1140.7</v>
       </c>
       <c r="P5" t="n">
-        <v>1125.74</v>
+        <v>1198.791891866258</v>
       </c>
       <c r="Q5" t="n">
         <v>1496</v>
@@ -4585,25 +4585,25 @@
         <v>1496</v>
       </c>
       <c r="S5" t="n">
-        <v>1407.751569573322</v>
+        <v>1409.632174038565</v>
       </c>
       <c r="T5" t="n">
-        <v>1221.021277892777</v>
+        <v>1222.884106610596</v>
       </c>
       <c r="U5" t="n">
-        <v>969.3160547407873</v>
+        <v>971.1785586019998</v>
       </c>
       <c r="V5" t="n">
-        <v>737.1433030571268</v>
+        <v>739.0058069183393</v>
       </c>
       <c r="W5" t="n">
-        <v>496.3620141874828</v>
+        <v>498.2245180486953</v>
       </c>
       <c r="X5" t="n">
-        <v>302.1379399847881</v>
+        <v>304.0004438460006</v>
       </c>
       <c r="Y5" t="n">
-        <v>189.6960887900342</v>
+        <v>191.5585926512467</v>
       </c>
     </row>
     <row r="6">
@@ -4613,76 +4613,76 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1092.253026833469</v>
+        <v>241.6095073802453</v>
       </c>
       <c r="C6" t="n">
-        <v>727.505640524864</v>
+        <v>241.6095073802453</v>
       </c>
       <c r="D6" t="n">
-        <v>376.0534315372855</v>
+        <v>241.6095073802453</v>
       </c>
       <c r="E6" t="n">
-        <v>29.92</v>
+        <v>241.6095073802453</v>
       </c>
       <c r="F6" t="n">
-        <v>29.92</v>
+        <v>241.6095073802453</v>
       </c>
       <c r="G6" t="n">
-        <v>29.92</v>
+        <v>241.6095073802453</v>
       </c>
       <c r="H6" t="n">
-        <v>29.92</v>
+        <v>241.6095073802453</v>
       </c>
       <c r="I6" t="n">
         <v>29.92</v>
       </c>
       <c r="J6" t="n">
-        <v>174.5985557413367</v>
+        <v>174.3973709300159</v>
       </c>
       <c r="K6" t="n">
-        <v>399.2086311753428</v>
+        <v>398.6635894772295</v>
       </c>
       <c r="L6" t="n">
-        <v>718.1819687139391</v>
+        <v>717.174568996958</v>
       </c>
       <c r="M6" t="n">
-        <v>859.8361604567983</v>
+        <v>858.2892107398172</v>
       </c>
       <c r="N6" t="n">
-        <v>1050.16096421531</v>
+        <v>1048.06018421531</v>
       </c>
       <c r="O6" t="n">
-        <v>1341.388006370727</v>
+        <v>1338.780579861293</v>
       </c>
       <c r="P6" t="n">
-        <v>1495.800085368536</v>
+        <v>1492.786030368536</v>
       </c>
       <c r="Q6" t="n">
-        <v>1495.800085368536</v>
+        <v>1492.786030368536</v>
       </c>
       <c r="R6" t="n">
-        <v>1360.932975467714</v>
+        <v>1357.784024336592</v>
       </c>
       <c r="S6" t="n">
-        <v>1297.853320462485</v>
+        <v>1294.664012937232</v>
       </c>
       <c r="T6" t="n">
-        <v>1293.343447077155</v>
+        <v>1290.14538216673</v>
       </c>
       <c r="U6" t="n">
-        <v>1293.145685169591</v>
+        <v>1289.947477320344</v>
       </c>
       <c r="V6" t="n">
-        <v>1278.488445582197</v>
+        <v>1275.29023773295</v>
       </c>
       <c r="W6" t="n">
-        <v>1245.788301228835</v>
+        <v>1242.590093379587</v>
       </c>
       <c r="X6" t="n">
-        <v>1092.253026833469</v>
+        <v>997.165062935801</v>
       </c>
       <c r="Y6" t="n">
-        <v>1092.253026833469</v>
+        <v>619.3872851580231</v>
       </c>
     </row>
     <row r="7">
@@ -4692,76 +4692,76 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>576.0083476291953</v>
+        <v>672.0456695795261</v>
       </c>
       <c r="C7" t="n">
-        <v>576.0083476291953</v>
+        <v>672.0456695795261</v>
       </c>
       <c r="D7" t="n">
-        <v>576.0083476291953</v>
+        <v>672.0456695795261</v>
       </c>
       <c r="E7" t="n">
-        <v>693.8372518406084</v>
+        <v>789.8745737909392</v>
       </c>
       <c r="F7" t="n">
-        <v>693.8372518406084</v>
+        <v>789.8745737909392</v>
       </c>
       <c r="G7" t="n">
-        <v>693.8372518406084</v>
+        <v>789.8745737909392</v>
       </c>
       <c r="H7" t="n">
-        <v>788.5444335226827</v>
+        <v>789.8745737909392</v>
       </c>
       <c r="I7" t="n">
-        <v>1015.207095409585</v>
+        <v>1016.483548464727</v>
       </c>
       <c r="J7" t="n">
-        <v>1385.467095409585</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="K7" t="n">
-        <v>1385.467095409585</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="L7" t="n">
-        <v>1385.467095409585</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="M7" t="n">
-        <v>1293.026305617309</v>
+        <v>1294.017231267251</v>
       </c>
       <c r="N7" t="n">
-        <v>1148.822122945132</v>
+        <v>1149.534310393385</v>
       </c>
       <c r="O7" t="n">
-        <v>932.4661797621563</v>
+        <v>932.9209073660642</v>
       </c>
       <c r="P7" t="n">
-        <v>664.8058098826245</v>
+        <v>665.0402361121327</v>
       </c>
       <c r="Q7" t="n">
-        <v>351.3853387456568</v>
+        <v>351.4672397226398</v>
       </c>
       <c r="R7" t="n">
         <v>29.92</v>
       </c>
       <c r="S7" t="n">
-        <v>29.92</v>
+        <v>70.34367574991084</v>
       </c>
       <c r="T7" t="n">
-        <v>29.92</v>
+        <v>70.34367574991084</v>
       </c>
       <c r="U7" t="n">
-        <v>29.92</v>
+        <v>125.9573219503309</v>
       </c>
       <c r="V7" t="n">
-        <v>29.92</v>
+        <v>125.9573219503309</v>
       </c>
       <c r="W7" t="n">
-        <v>201.8109182596774</v>
+        <v>297.8482402100083</v>
       </c>
       <c r="X7" t="n">
-        <v>352.841709283871</v>
+        <v>448.8790312342018</v>
       </c>
       <c r="Y7" t="n">
-        <v>464.2510099629032</v>
+        <v>560.2883319132341</v>
       </c>
     </row>
     <row r="8">
@@ -4771,49 +4771,49 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>108.8416377852028</v>
+        <v>108.731003807232</v>
       </c>
       <c r="C8" t="n">
-        <v>56.89417848844992</v>
+        <v>58.7566823496624</v>
       </c>
       <c r="D8" t="n">
-        <v>46.450586832036</v>
+        <v>48.31309069324847</v>
       </c>
       <c r="E8" t="n">
-        <v>42.04322359277474</v>
+        <v>43.90572745398721</v>
       </c>
       <c r="F8" t="n">
-        <v>37.10420469579307</v>
+        <v>38.96670855700554</v>
       </c>
       <c r="G8" t="n">
-        <v>33.72713203391686</v>
+        <v>35.58557518755106</v>
       </c>
       <c r="H8" t="n">
-        <v>29.92</v>
+        <v>31.736856432148</v>
       </c>
       <c r="I8" t="n">
         <v>29.92</v>
       </c>
       <c r="J8" t="n">
-        <v>30.01969029977264</v>
+        <v>29.92</v>
       </c>
       <c r="K8" t="n">
-        <v>400.2796902997726</v>
+        <v>400.18</v>
       </c>
       <c r="L8" t="n">
-        <v>770.5396902997726</v>
+        <v>770.4399999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>1067.075793611129</v>
+        <v>770.4399999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>1437.335793611129</v>
+        <v>1067.648108133742</v>
       </c>
       <c r="O8" t="n">
-        <v>1437.335793611129</v>
+        <v>1067.648108133742</v>
       </c>
       <c r="P8" t="n">
-        <v>1496</v>
+        <v>1125.74</v>
       </c>
       <c r="Q8" t="n">
         <v>1496</v>
@@ -4822,25 +4822,25 @@
         <v>1496</v>
       </c>
       <c r="S8" t="n">
-        <v>1409.724707412506</v>
+        <v>1409.632174038565</v>
       </c>
       <c r="T8" t="n">
-        <v>1222.994415731961</v>
+        <v>1222.884106610596</v>
       </c>
       <c r="U8" t="n">
-        <v>971.2891925799706</v>
+        <v>971.1785586019998</v>
       </c>
       <c r="V8" t="n">
-        <v>739.1164408963101</v>
+        <v>739.0058069183393</v>
       </c>
       <c r="W8" t="n">
-        <v>498.3351520266661</v>
+        <v>498.2245180486953</v>
       </c>
       <c r="X8" t="n">
-        <v>304.1110778239714</v>
+        <v>304.0004438460006</v>
       </c>
       <c r="Y8" t="n">
-        <v>191.6692266292175</v>
+        <v>191.5585926512467</v>
       </c>
     </row>
     <row r="9">
@@ -4850,76 +4850,76 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1225.724928051676</v>
+        <v>156.6141439870103</v>
       </c>
       <c r="C9" t="n">
-        <v>1070.572551977265</v>
+        <v>156.6141439870103</v>
       </c>
       <c r="D9" t="n">
-        <v>719.1203429896864</v>
+        <v>156.6141439870103</v>
       </c>
       <c r="E9" t="n">
-        <v>372.9869114524009</v>
+        <v>156.6141439870103</v>
       </c>
       <c r="F9" t="n">
-        <v>29.92</v>
+        <v>156.6141439870103</v>
       </c>
       <c r="G9" t="n">
-        <v>29.92</v>
+        <v>156.6141439870103</v>
       </c>
       <c r="H9" t="n">
-        <v>29.92</v>
+        <v>156.6141439870103</v>
       </c>
       <c r="I9" t="n">
         <v>29.92</v>
       </c>
       <c r="J9" t="n">
-        <v>174.5985557413367</v>
+        <v>174.3973709300159</v>
       </c>
       <c r="K9" t="n">
-        <v>399.2086311753428</v>
+        <v>398.6635894772295</v>
       </c>
       <c r="L9" t="n">
-        <v>718.1819687139391</v>
+        <v>717.174568996958</v>
       </c>
       <c r="M9" t="n">
-        <v>859.8361604567983</v>
+        <v>858.2892107398172</v>
       </c>
       <c r="N9" t="n">
-        <v>1050.16096421531</v>
+        <v>1048.06018421531</v>
       </c>
       <c r="O9" t="n">
-        <v>1341.388006370727</v>
+        <v>1338.780579861293</v>
       </c>
       <c r="P9" t="n">
-        <v>1495.800085368536</v>
+        <v>1492.786030368536</v>
       </c>
       <c r="Q9" t="n">
-        <v>1495.800085368536</v>
+        <v>1492.786030368536</v>
       </c>
       <c r="R9" t="n">
-        <v>1360.932975467714</v>
+        <v>1357.784024336592</v>
       </c>
       <c r="S9" t="n">
-        <v>1297.853320462485</v>
+        <v>1294.664012937232</v>
       </c>
       <c r="T9" t="n">
-        <v>1293.343447077155</v>
+        <v>1290.14538216673</v>
       </c>
       <c r="U9" t="n">
-        <v>1293.145685169591</v>
+        <v>1289.947477320344</v>
       </c>
       <c r="V9" t="n">
-        <v>1278.488445582197</v>
+        <v>912.1696995425659</v>
       </c>
       <c r="W9" t="n">
-        <v>1245.788301228835</v>
+        <v>534.3919217647881</v>
       </c>
       <c r="X9" t="n">
-        <v>1225.724928051676</v>
+        <v>156.6141439870103</v>
       </c>
       <c r="Y9" t="n">
-        <v>1225.724928051676</v>
+        <v>156.6141439870103</v>
       </c>
     </row>
     <row r="10">
@@ -4929,76 +4929,76 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>70.37478771712392</v>
+        <v>1147.422398521291</v>
       </c>
       <c r="C10" t="n">
-        <v>70.37478771712392</v>
+        <v>1273.424404339727</v>
       </c>
       <c r="D10" t="n">
-        <v>85.85883935008918</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="E10" t="n">
-        <v>203.6877435615022</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="F10" t="n">
-        <v>328.0487161534377</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="G10" t="n">
-        <v>481.6391623681918</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="H10" t="n">
-        <v>652.7906108062779</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="I10" t="n">
-        <v>879.4532726931805</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="J10" t="n">
-        <v>1249.71327269318</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="K10" t="n">
-        <v>1381.441257449721</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="L10" t="n">
-        <v>1385.467095409585</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="M10" t="n">
-        <v>1293.026305617309</v>
+        <v>1294.017231267251</v>
       </c>
       <c r="N10" t="n">
-        <v>1148.822122945132</v>
+        <v>1149.534310393385</v>
       </c>
       <c r="O10" t="n">
-        <v>932.4661797621563</v>
+        <v>932.9209073660642</v>
       </c>
       <c r="P10" t="n">
-        <v>664.8058098826245</v>
+        <v>665.0402361121327</v>
       </c>
       <c r="Q10" t="n">
-        <v>351.3853387456568</v>
+        <v>351.4672397226398</v>
       </c>
       <c r="R10" t="n">
         <v>29.92</v>
       </c>
       <c r="S10" t="n">
-        <v>70.37478771712392</v>
+        <v>29.92</v>
       </c>
       <c r="T10" t="n">
-        <v>70.37478771712392</v>
+        <v>155.9515329088468</v>
       </c>
       <c r="U10" t="n">
-        <v>70.37478771712392</v>
+        <v>402.5126580061498</v>
       </c>
       <c r="V10" t="n">
-        <v>70.37478771712392</v>
+        <v>601.3340508920958</v>
       </c>
       <c r="W10" t="n">
-        <v>70.37478771712392</v>
+        <v>773.2249691517732</v>
       </c>
       <c r="X10" t="n">
-        <v>70.37478771712392</v>
+        <v>924.2557601759667</v>
       </c>
       <c r="Y10" t="n">
-        <v>70.37478771712392</v>
+        <v>1035.665060854999</v>
       </c>
     </row>
     <row r="11">
@@ -5008,25 +5008,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>596.6553483293503</v>
+        <v>597.1205880922942</v>
       </c>
       <c r="C11" t="n">
-        <v>466.8830470738009</v>
+        <v>467.3482868367447</v>
       </c>
       <c r="D11" t="n">
-        <v>376.6414756194072</v>
+        <v>377.106715382351</v>
       </c>
       <c r="E11" t="n">
-        <v>292.4361325821661</v>
+        <v>292.9013723451099</v>
       </c>
       <c r="F11" t="n">
-        <v>207.6991338872047</v>
+        <v>208.1643736501484</v>
       </c>
       <c r="G11" t="n">
-        <v>125.5027119537179</v>
+        <v>125.9679517166617</v>
       </c>
       <c r="H11" t="n">
-        <v>51.92</v>
+        <v>52.3852397629438</v>
       </c>
       <c r="I11" t="n">
         <v>51.92</v>
@@ -5035,49 +5035,49 @@
         <v>559.4285273090126</v>
       </c>
       <c r="K11" t="n">
-        <v>733.5813277110226</v>
+        <v>1201.938527309012</v>
       </c>
       <c r="L11" t="n">
-        <v>949.6332762537361</v>
+        <v>1792.359898617045</v>
       </c>
       <c r="M11" t="n">
-        <v>949.6332762537362</v>
+        <v>1792.359898617045</v>
       </c>
       <c r="N11" t="n">
-        <v>949.6332762537362</v>
+        <v>1792.359898617045</v>
       </c>
       <c r="O11" t="n">
-        <v>1367.045081027735</v>
+        <v>1953.49</v>
       </c>
       <c r="P11" t="n">
-        <v>2009.555081027735</v>
+        <v>2596</v>
       </c>
       <c r="Q11" t="n">
         <v>2596</v>
       </c>
       <c r="R11" t="n">
-        <v>2595.534760237057</v>
+        <v>2596</v>
       </c>
       <c r="S11" t="n">
-        <v>2451.762030971221</v>
+        <v>2452.227270734164</v>
       </c>
       <c r="T11" t="n">
-        <v>2189.517714621877</v>
+        <v>2189.982954384821</v>
       </c>
       <c r="U11" t="n">
-        <v>1858.092802114017</v>
+        <v>1858.558041876961</v>
       </c>
       <c r="V11" t="n">
-        <v>1546.122070632377</v>
+        <v>1546.587310395321</v>
       </c>
       <c r="W11" t="n">
-        <v>1225.542801964753</v>
+        <v>1226.008041727697</v>
       </c>
       <c r="X11" t="n">
-        <v>951.5207479640785</v>
+        <v>951.9859877270223</v>
       </c>
       <c r="Y11" t="n">
-        <v>759.2809169713448</v>
+        <v>759.7461567342887</v>
       </c>
     </row>
     <row r="12">
@@ -5087,25 +5087,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>492.6952769985969</v>
+        <v>686.2820590119658</v>
       </c>
       <c r="C12" t="n">
-        <v>452.1903149324158</v>
+        <v>645.7770969457847</v>
       </c>
       <c r="D12" t="n">
-        <v>424.9805301872616</v>
+        <v>618.5673122006306</v>
       </c>
       <c r="E12" t="n">
-        <v>403.0895228924003</v>
+        <v>596.6763049057694</v>
       </c>
       <c r="F12" t="n">
-        <v>60.0226114399994</v>
+        <v>577.8518176957928</v>
       </c>
       <c r="G12" t="n">
-        <v>55.98259997866058</v>
+        <v>573.8118062344539</v>
       </c>
       <c r="H12" t="n">
-        <v>51.92</v>
+        <v>245.506782013369</v>
       </c>
       <c r="I12" t="n">
         <v>51.92</v>
@@ -5144,19 +5144,19 @@
         <v>1846.683151095641</v>
       </c>
       <c r="U12" t="n">
-        <v>1766.721857646244</v>
+        <v>1442.479433403819</v>
       </c>
       <c r="V12" t="n">
-        <v>1672.26663826087</v>
+        <v>1348.024214018445</v>
       </c>
       <c r="W12" t="n">
-        <v>1559.768514109528</v>
+        <v>1235.526089867103</v>
       </c>
       <c r="X12" t="n">
-        <v>1135.664736891964</v>
+        <v>829.6638260952597</v>
       </c>
       <c r="Y12" t="n">
-        <v>732.2390876332428</v>
+        <v>750.4806010789623</v>
       </c>
     </row>
     <row r="13">
@@ -5196,16 +5196,16 @@
         <v>1619.080700024145</v>
       </c>
       <c r="L13" t="n">
-        <v>1609.501360385148</v>
+        <v>1608.654647405756</v>
       </c>
       <c r="M13" t="n">
-        <v>1506.07469544798</v>
+        <v>1505.227982468588</v>
       </c>
       <c r="N13" t="n">
-        <v>1349.248439584877</v>
+        <v>1348.401726605486</v>
       </c>
       <c r="O13" t="n">
-        <v>1115.142339091088</v>
+        <v>1114.295626111697</v>
       </c>
       <c r="P13" t="n">
         <v>820.7766206439126</v>
@@ -5245,22 +5245,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>596.6553483293503</v>
+        <v>597.1205880922942</v>
       </c>
       <c r="C14" t="n">
-        <v>466.8830470738009</v>
+        <v>467.3482868367447</v>
       </c>
       <c r="D14" t="n">
-        <v>376.6414756194072</v>
+        <v>377.106715382351</v>
       </c>
       <c r="E14" t="n">
-        <v>292.4361325821661</v>
+        <v>292.9013723451099</v>
       </c>
       <c r="F14" t="n">
-        <v>207.6991338872047</v>
+        <v>208.1643736501484</v>
       </c>
       <c r="G14" t="n">
-        <v>125.5027119537179</v>
+        <v>125.9679517166617</v>
       </c>
       <c r="H14" t="n">
         <v>51.92</v>
@@ -5275,16 +5275,16 @@
         <v>733.5813277110226</v>
       </c>
       <c r="L14" t="n">
-        <v>1009.32297330616</v>
+        <v>1205.91497964478</v>
       </c>
       <c r="M14" t="n">
-        <v>1009.32297330616</v>
+        <v>1205.91497964478</v>
       </c>
       <c r="N14" t="n">
-        <v>1651.83297330616</v>
+        <v>1205.91497964478</v>
       </c>
       <c r="O14" t="n">
-        <v>1812.963074689115</v>
+        <v>1367.045081027735</v>
       </c>
       <c r="P14" t="n">
         <v>2009.555081027735</v>
@@ -5296,25 +5296,25 @@
         <v>2596</v>
       </c>
       <c r="S14" t="n">
-        <v>2451.762030971221</v>
+        <v>2452.227270734164</v>
       </c>
       <c r="T14" t="n">
-        <v>2189.517714621877</v>
+        <v>2189.982954384821</v>
       </c>
       <c r="U14" t="n">
-        <v>1858.092802114017</v>
+        <v>1858.558041876961</v>
       </c>
       <c r="V14" t="n">
-        <v>1546.122070632377</v>
+        <v>1546.587310395321</v>
       </c>
       <c r="W14" t="n">
-        <v>1225.542801964753</v>
+        <v>1226.008041727697</v>
       </c>
       <c r="X14" t="n">
-        <v>951.5207479640785</v>
+        <v>951.9859877270223</v>
       </c>
       <c r="Y14" t="n">
-        <v>759.2809169713448</v>
+        <v>759.7461567342887</v>
       </c>
     </row>
     <row r="15">
@@ -5324,19 +5324,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1141.180125483445</v>
+        <v>1316.525394051095</v>
       </c>
       <c r="C15" t="n">
-        <v>1100.675163417264</v>
+        <v>1276.020431984914</v>
       </c>
       <c r="D15" t="n">
-        <v>1073.46537867211</v>
+        <v>924.5682229973352</v>
       </c>
       <c r="E15" t="n">
-        <v>727.3319471348245</v>
+        <v>578.4347914600496</v>
       </c>
       <c r="F15" t="n">
-        <v>384.2650356824237</v>
+        <v>235.3678800076487</v>
       </c>
       <c r="G15" t="n">
         <v>55.98259997866058</v>
@@ -5393,7 +5393,7 @@
         <v>1459.907161134389</v>
       </c>
       <c r="Y15" t="n">
-        <v>1205.378667550442</v>
+        <v>1380.723936118091</v>
       </c>
     </row>
     <row r="16">
@@ -5494,37 +5494,37 @@
         <v>292.9013723451099</v>
       </c>
       <c r="F17" t="n">
-        <v>208.1643736501484</v>
+        <v>207.6991338872047</v>
       </c>
       <c r="G17" t="n">
-        <v>125.9679517166617</v>
+        <v>125.5027119537179</v>
       </c>
       <c r="H17" t="n">
-        <v>52.3852397629438</v>
+        <v>51.92</v>
       </c>
       <c r="I17" t="n">
         <v>51.92</v>
       </c>
       <c r="J17" t="n">
-        <v>559.4285273090126</v>
+        <v>133.4268380887174</v>
       </c>
       <c r="K17" t="n">
-        <v>793.271024763446</v>
+        <v>775.9368380887173</v>
       </c>
       <c r="L17" t="n">
-        <v>1009.32297330616</v>
+        <v>1418.446838088717</v>
       </c>
       <c r="M17" t="n">
-        <v>1009.32297330616</v>
+        <v>2060.956838088718</v>
       </c>
       <c r="N17" t="n">
-        <v>1651.83297330616</v>
+        <v>2238.277892278425</v>
       </c>
       <c r="O17" t="n">
-        <v>1812.963074689115</v>
+        <v>2399.40799366138</v>
       </c>
       <c r="P17" t="n">
-        <v>2009.555081027735</v>
+        <v>2596</v>
       </c>
       <c r="Q17" t="n">
         <v>2596</v>
@@ -5746,13 +5746,13 @@
         <v>133.4268380887174</v>
       </c>
       <c r="K20" t="n">
-        <v>310.7478922784251</v>
+        <v>775.9368380887173</v>
       </c>
       <c r="L20" t="n">
-        <v>953.2578922784251</v>
+        <v>1418.446838088717</v>
       </c>
       <c r="M20" t="n">
-        <v>1595.767892278425</v>
+        <v>2060.956838088718</v>
       </c>
       <c r="N20" t="n">
         <v>2238.277892278425</v>
@@ -5798,16 +5798,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>168.4528527561725</v>
+        <v>1316.525394051095</v>
       </c>
       <c r="C21" t="n">
-        <v>127.9478906899915</v>
+        <v>1100.675163417264</v>
       </c>
       <c r="D21" t="n">
-        <v>100.7381059448373</v>
+        <v>749.2229544296858</v>
       </c>
       <c r="E21" t="n">
-        <v>78.84709864997603</v>
+        <v>403.0895228924003</v>
       </c>
       <c r="F21" t="n">
         <v>60.0226114399994</v>
@@ -5858,16 +5858,16 @@
         <v>1766.721857646244</v>
       </c>
       <c r="V21" t="n">
-        <v>1348.024214018445</v>
+        <v>1672.26663826087</v>
       </c>
       <c r="W21" t="n">
-        <v>911.2836656246791</v>
+        <v>1559.768514109528</v>
       </c>
       <c r="X21" t="n">
-        <v>487.1798884071159</v>
+        <v>1459.907161134389</v>
       </c>
       <c r="Y21" t="n">
-        <v>232.6513948231691</v>
+        <v>1380.723936118091</v>
       </c>
     </row>
     <row r="22">
@@ -5907,25 +5907,25 @@
         <v>1619.080700024145</v>
       </c>
       <c r="L22" t="n">
-        <v>1608.654647405756</v>
+        <v>1609.501360385148</v>
       </c>
       <c r="M22" t="n">
-        <v>1505.227982468588</v>
+        <v>1506.07469544798</v>
       </c>
       <c r="N22" t="n">
-        <v>1348.401726605486</v>
+        <v>1349.248439584877</v>
       </c>
       <c r="O22" t="n">
-        <v>1114.295626111697</v>
+        <v>1115.142339091088</v>
       </c>
       <c r="P22" t="n">
-        <v>819.9299076645211</v>
+        <v>820.7766206439126</v>
       </c>
       <c r="Q22" t="n">
-        <v>463.4700425881595</v>
+        <v>464.3167555675508</v>
       </c>
       <c r="R22" t="n">
-        <v>81.94485949741244</v>
+        <v>82.79157247680381</v>
       </c>
       <c r="S22" t="n">
         <v>51.92</v>
@@ -5968,13 +5968,13 @@
         <v>292.9013723451097</v>
       </c>
       <c r="F23" t="n">
-        <v>207.6991338872046</v>
+        <v>208.1643736501482</v>
       </c>
       <c r="G23" t="n">
-        <v>125.5027119537179</v>
+        <v>125.9679517166614</v>
       </c>
       <c r="H23" t="n">
-        <v>51.92</v>
+        <v>52.38523976294358</v>
       </c>
       <c r="I23" t="n">
         <v>51.92</v>
@@ -5983,22 +5983,22 @@
         <v>133.4268380887174</v>
       </c>
       <c r="K23" t="n">
-        <v>307.5796384907274</v>
+        <v>366.8129733061596</v>
       </c>
       <c r="L23" t="n">
-        <v>523.631587033441</v>
+        <v>1009.32297330616</v>
       </c>
       <c r="M23" t="n">
-        <v>1149.849898617045</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="N23" t="n">
-        <v>1792.359898617045</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="O23" t="n">
-        <v>1953.49</v>
+        <v>1812.963074689115</v>
       </c>
       <c r="P23" t="n">
-        <v>2596</v>
+        <v>2009.555081027735</v>
       </c>
       <c r="Q23" t="n">
         <v>2596</v>
@@ -6035,7 +6035,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>168.4528527561725</v>
+        <v>492.6952769985968</v>
       </c>
       <c r="C24" t="n">
         <v>127.9478906899915</v>
@@ -6089,22 +6089,22 @@
         <v>1928.880474452383</v>
       </c>
       <c r="T24" t="n">
-        <v>1671.337882527992</v>
+        <v>1846.683151095642</v>
       </c>
       <c r="U24" t="n">
-        <v>1591.376589078594</v>
+        <v>1766.721857646244</v>
       </c>
       <c r="V24" t="n">
-        <v>1172.678945450796</v>
+        <v>1672.26663826087</v>
       </c>
       <c r="W24" t="n">
-        <v>735.9383970570298</v>
+        <v>1559.768514109528</v>
       </c>
       <c r="X24" t="n">
-        <v>311.8346198394665</v>
+        <v>1284.561892566739</v>
       </c>
       <c r="Y24" t="n">
-        <v>232.6513948231691</v>
+        <v>881.1362433080176</v>
       </c>
     </row>
     <row r="25">
@@ -6193,40 +6193,40 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>597.1205880922942</v>
+        <v>596.6553483293503</v>
       </c>
       <c r="C26" t="n">
-        <v>467.3482868367447</v>
+        <v>466.8830470738009</v>
       </c>
       <c r="D26" t="n">
-        <v>377.106715382351</v>
+        <v>376.6414756194072</v>
       </c>
       <c r="E26" t="n">
-        <v>292.9013723451099</v>
+        <v>292.4361325821661</v>
       </c>
       <c r="F26" t="n">
-        <v>208.1643736501484</v>
+        <v>207.6991338872046</v>
       </c>
       <c r="G26" t="n">
-        <v>125.9679517166617</v>
+        <v>125.5027119537179</v>
       </c>
       <c r="H26" t="n">
-        <v>52.3852397629438</v>
+        <v>51.92</v>
       </c>
       <c r="I26" t="n">
         <v>51.92</v>
       </c>
       <c r="J26" t="n">
-        <v>133.4268380887174</v>
+        <v>559.4285273090126</v>
       </c>
       <c r="K26" t="n">
-        <v>775.9368380887173</v>
+        <v>1201.938527309012</v>
       </c>
       <c r="L26" t="n">
-        <v>1418.446838088717</v>
+        <v>1844.448527309012</v>
       </c>
       <c r="M26" t="n">
-        <v>1595.767892278425</v>
+        <v>2238.277892278425</v>
       </c>
       <c r="N26" t="n">
         <v>2238.277892278425</v>
@@ -6241,28 +6241,28 @@
         <v>2596</v>
       </c>
       <c r="R26" t="n">
-        <v>2596</v>
+        <v>2595.534760237057</v>
       </c>
       <c r="S26" t="n">
-        <v>2452.227270734164</v>
+        <v>2451.762030971221</v>
       </c>
       <c r="T26" t="n">
-        <v>2189.982954384821</v>
+        <v>2189.517714621877</v>
       </c>
       <c r="U26" t="n">
-        <v>1858.558041876961</v>
+        <v>1858.092802114017</v>
       </c>
       <c r="V26" t="n">
-        <v>1546.587310395321</v>
+        <v>1546.122070632377</v>
       </c>
       <c r="W26" t="n">
-        <v>1226.008041727697</v>
+        <v>1225.542801964753</v>
       </c>
       <c r="X26" t="n">
-        <v>951.9859877270223</v>
+        <v>951.5207479640785</v>
       </c>
       <c r="Y26" t="n">
-        <v>759.7461567342887</v>
+        <v>759.2809169713448</v>
       </c>
     </row>
     <row r="27">
@@ -6272,25 +6272,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>686.2820590119658</v>
+        <v>492.6952769985969</v>
       </c>
       <c r="C27" t="n">
-        <v>645.7770969457847</v>
+        <v>452.1903149324158</v>
       </c>
       <c r="D27" t="n">
-        <v>618.5673122006306</v>
+        <v>424.9805301872616</v>
       </c>
       <c r="E27" t="n">
-        <v>596.6763049057694</v>
+        <v>403.0895228924003</v>
       </c>
       <c r="F27" t="n">
-        <v>577.8518176957928</v>
+        <v>384.2650356824237</v>
       </c>
       <c r="G27" t="n">
-        <v>573.8118062344539</v>
+        <v>380.2250242210849</v>
       </c>
       <c r="H27" t="n">
-        <v>245.506782013369</v>
+        <v>51.92</v>
       </c>
       <c r="I27" t="n">
         <v>51.92</v>
@@ -6326,22 +6326,22 @@
         <v>1928.880474452383</v>
       </c>
       <c r="T27" t="n">
-        <v>1846.683151095641</v>
+        <v>1846.683151095642</v>
       </c>
       <c r="U27" t="n">
-        <v>1766.721857646244</v>
+        <v>1591.376589078594</v>
       </c>
       <c r="V27" t="n">
-        <v>1672.26663826087</v>
+        <v>1496.92136969322</v>
       </c>
       <c r="W27" t="n">
-        <v>1559.768514109528</v>
+        <v>1060.180821299454</v>
       </c>
       <c r="X27" t="n">
-        <v>1135.664736891964</v>
+        <v>960.3194683243152</v>
       </c>
       <c r="Y27" t="n">
-        <v>750.4806010789623</v>
+        <v>881.1362433080178</v>
       </c>
     </row>
     <row r="28">
@@ -6396,7 +6396,7 @@
         <v>820.7766206439126</v>
       </c>
       <c r="Q28" t="n">
-        <v>464.3167555675508</v>
+        <v>464.3167555675509</v>
       </c>
       <c r="R28" t="n">
         <v>82.79157247680381</v>
@@ -6430,49 +6430,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>597.1205880922939</v>
+        <v>597.1205880922942</v>
       </c>
       <c r="C29" t="n">
-        <v>467.3482868367445</v>
+        <v>467.3482868367447</v>
       </c>
       <c r="D29" t="n">
-        <v>377.1067153823507</v>
+        <v>377.106715382351</v>
       </c>
       <c r="E29" t="n">
-        <v>292.9013723451097</v>
+        <v>292.9013723451099</v>
       </c>
       <c r="F29" t="n">
-        <v>207.6991338872046</v>
+        <v>208.1643736501484</v>
       </c>
       <c r="G29" t="n">
-        <v>125.5027119537179</v>
+        <v>125.9679517166617</v>
       </c>
       <c r="H29" t="n">
-        <v>51.92</v>
+        <v>52.3852397629438</v>
       </c>
       <c r="I29" t="n">
         <v>51.92</v>
       </c>
       <c r="J29" t="n">
-        <v>559.4285273090126</v>
+        <v>133.4268380887174</v>
       </c>
       <c r="K29" t="n">
-        <v>737.2059437357115</v>
+        <v>307.5796384907274</v>
       </c>
       <c r="L29" t="n">
-        <v>953.2578922784251</v>
+        <v>523.631587033441</v>
       </c>
       <c r="M29" t="n">
-        <v>1595.767892278425</v>
+        <v>1166.141587033441</v>
       </c>
       <c r="N29" t="n">
-        <v>2238.277892278425</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="O29" t="n">
-        <v>2399.40799366138</v>
+        <v>1812.963074689115</v>
       </c>
       <c r="P29" t="n">
-        <v>2596</v>
+        <v>2009.555081027735</v>
       </c>
       <c r="Q29" t="n">
         <v>2596</v>
@@ -6490,16 +6490,16 @@
         <v>1858.558041876961</v>
       </c>
       <c r="V29" t="n">
-        <v>1546.58731039532</v>
+        <v>1546.587310395321</v>
       </c>
       <c r="W29" t="n">
         <v>1226.008041727697</v>
       </c>
       <c r="X29" t="n">
-        <v>951.9859877270221</v>
+        <v>951.9859877270223</v>
       </c>
       <c r="Y29" t="n">
-        <v>759.7461567342884</v>
+        <v>759.7461567342887</v>
       </c>
     </row>
     <row r="30">
@@ -6509,22 +6509,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>992.2829698086708</v>
+        <v>168.4528527561725</v>
       </c>
       <c r="C30" t="n">
-        <v>951.7780077424898</v>
+        <v>127.9478906899915</v>
       </c>
       <c r="D30" t="n">
-        <v>924.5682229973356</v>
+        <v>100.7381059448373</v>
       </c>
       <c r="E30" t="n">
-        <v>902.6772157024744</v>
+        <v>78.84709864997603</v>
       </c>
       <c r="F30" t="n">
-        <v>559.6103042500736</v>
+        <v>60.0226114399994</v>
       </c>
       <c r="G30" t="n">
-        <v>380.2250242210849</v>
+        <v>55.98259997866058</v>
       </c>
       <c r="H30" t="n">
         <v>51.92</v>
@@ -6563,22 +6563,22 @@
         <v>1928.880474452383</v>
       </c>
       <c r="T30" t="n">
-        <v>1846.683151095642</v>
+        <v>1846.683151095641</v>
       </c>
       <c r="U30" t="n">
-        <v>1442.479433403819</v>
+        <v>1766.721857646244</v>
       </c>
       <c r="V30" t="n">
-        <v>1348.024214018445</v>
+        <v>1496.92136969322</v>
       </c>
       <c r="W30" t="n">
-        <v>1235.526089867104</v>
+        <v>1060.180821299454</v>
       </c>
       <c r="X30" t="n">
-        <v>1135.664736891965</v>
+        <v>636.0770440818908</v>
       </c>
       <c r="Y30" t="n">
-        <v>1056.481511875667</v>
+        <v>232.6513948231691</v>
       </c>
     </row>
     <row r="31">
@@ -6627,13 +6627,13 @@
         <v>1348.401726605486</v>
       </c>
       <c r="O31" t="n">
-        <v>1114.295626111697</v>
+        <v>1115.142339091088</v>
       </c>
       <c r="P31" t="n">
-        <v>819.9299076645212</v>
+        <v>820.7766206439126</v>
       </c>
       <c r="Q31" t="n">
-        <v>464.3167555675509</v>
+        <v>464.3167555675508</v>
       </c>
       <c r="R31" t="n">
         <v>82.79157247680381</v>
@@ -6667,49 +6667,49 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>597.1205880922939</v>
+        <v>596.6553483293503</v>
       </c>
       <c r="C32" t="n">
-        <v>467.3482868367445</v>
+        <v>466.8830470738009</v>
       </c>
       <c r="D32" t="n">
-        <v>377.1067153823507</v>
+        <v>376.6414756194072</v>
       </c>
       <c r="E32" t="n">
-        <v>292.9013723451097</v>
+        <v>292.4361325821661</v>
       </c>
       <c r="F32" t="n">
-        <v>208.1643736501482</v>
+        <v>207.6991338872046</v>
       </c>
       <c r="G32" t="n">
-        <v>125.9679517166614</v>
+        <v>125.5027119537179</v>
       </c>
       <c r="H32" t="n">
-        <v>52.38523976294358</v>
+        <v>51.92</v>
       </c>
       <c r="I32" t="n">
         <v>51.92</v>
       </c>
       <c r="J32" t="n">
-        <v>133.4268380887174</v>
+        <v>559.4285273090126</v>
       </c>
       <c r="K32" t="n">
-        <v>775.9368380887173</v>
+        <v>733.5813277110226</v>
       </c>
       <c r="L32" t="n">
-        <v>1418.446838088717</v>
+        <v>949.6332762537361</v>
       </c>
       <c r="M32" t="n">
-        <v>1595.767892278425</v>
+        <v>1592.143276253736</v>
       </c>
       <c r="N32" t="n">
-        <v>2238.277892278425</v>
+        <v>2234.653276253736</v>
       </c>
       <c r="O32" t="n">
-        <v>2399.40799366138</v>
+        <v>2395.783377636692</v>
       </c>
       <c r="P32" t="n">
-        <v>2596</v>
+        <v>2592.375383975311</v>
       </c>
       <c r="Q32" t="n">
         <v>2596</v>
@@ -6736,7 +6736,7 @@
         <v>951.9859877270221</v>
       </c>
       <c r="Y32" t="n">
-        <v>759.7461567342884</v>
+        <v>759.2809169713448</v>
       </c>
     </row>
     <row r="33">
@@ -6746,19 +6746,19 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1141.180125483445</v>
+        <v>343.7981213238224</v>
       </c>
       <c r="C33" t="n">
-        <v>1100.675163417264</v>
+        <v>303.2931592576413</v>
       </c>
       <c r="D33" t="n">
-        <v>749.2229544296858</v>
+        <v>276.0833745124871</v>
       </c>
       <c r="E33" t="n">
-        <v>403.0895228924003</v>
+        <v>254.1923672176258</v>
       </c>
       <c r="F33" t="n">
-        <v>60.02261143999941</v>
+        <v>235.3678800076492</v>
       </c>
       <c r="G33" t="n">
         <v>55.98259997866057</v>
@@ -6794,28 +6794,28 @@
         <v>2244.187340368535</v>
       </c>
       <c r="R33" t="n">
-        <v>2062.032218270268</v>
+        <v>1737.789794027844</v>
       </c>
       <c r="S33" t="n">
-        <v>1928.880474452383</v>
+        <v>1604.638050209959</v>
       </c>
       <c r="T33" t="n">
-        <v>1846.683151095642</v>
+        <v>1522.440726853217</v>
       </c>
       <c r="U33" t="n">
-        <v>1766.721857646244</v>
+        <v>1442.47943340382</v>
       </c>
       <c r="V33" t="n">
-        <v>1672.26663826087</v>
+        <v>1348.024214018446</v>
       </c>
       <c r="W33" t="n">
-        <v>1384.423245541878</v>
+        <v>911.2836656246795</v>
       </c>
       <c r="X33" t="n">
-        <v>1284.561892566739</v>
+        <v>487.1798884071163</v>
       </c>
       <c r="Y33" t="n">
-        <v>1205.378667550442</v>
+        <v>407.996663390819</v>
       </c>
     </row>
     <row r="34">
@@ -6904,34 +6904,34 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>596.6553483293503</v>
+        <v>597.1205880922939</v>
       </c>
       <c r="C35" t="n">
-        <v>466.8830470738009</v>
+        <v>467.3482868367445</v>
       </c>
       <c r="D35" t="n">
-        <v>376.6414756194072</v>
+        <v>377.1067153823507</v>
       </c>
       <c r="E35" t="n">
-        <v>292.4361325821661</v>
+        <v>292.9013723451097</v>
       </c>
       <c r="F35" t="n">
-        <v>207.6991338872047</v>
+        <v>208.1643736501482</v>
       </c>
       <c r="G35" t="n">
-        <v>125.5027119537179</v>
+        <v>125.9679517166614</v>
       </c>
       <c r="H35" t="n">
-        <v>51.92</v>
+        <v>52.38523976294358</v>
       </c>
       <c r="I35" t="n">
         <v>51.92</v>
       </c>
       <c r="J35" t="n">
-        <v>133.4268380887174</v>
+        <v>559.4285273090126</v>
       </c>
       <c r="K35" t="n">
-        <v>775.9368380887173</v>
+        <v>733.5813277110226</v>
       </c>
       <c r="L35" t="n">
         <v>1009.32297330616</v>
@@ -6952,28 +6952,28 @@
         <v>2596</v>
       </c>
       <c r="R35" t="n">
-        <v>2595.534760237057</v>
+        <v>2596</v>
       </c>
       <c r="S35" t="n">
-        <v>2451.762030971221</v>
+        <v>2452.227270734164</v>
       </c>
       <c r="T35" t="n">
-        <v>2189.517714621877</v>
+        <v>2189.982954384821</v>
       </c>
       <c r="U35" t="n">
-        <v>1858.092802114017</v>
+        <v>1858.558041876961</v>
       </c>
       <c r="V35" t="n">
-        <v>1546.122070632377</v>
+        <v>1546.58731039532</v>
       </c>
       <c r="W35" t="n">
-        <v>1225.542801964753</v>
+        <v>1226.008041727697</v>
       </c>
       <c r="X35" t="n">
-        <v>951.5207479640785</v>
+        <v>951.9859877270221</v>
       </c>
       <c r="Y35" t="n">
-        <v>759.2809169713448</v>
+        <v>759.7461567342884</v>
       </c>
     </row>
     <row r="36">
@@ -6983,22 +6983,22 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>492.6952769985968</v>
+        <v>992.2829698086708</v>
       </c>
       <c r="C36" t="n">
-        <v>127.9478906899915</v>
+        <v>951.7780077424898</v>
       </c>
       <c r="D36" t="n">
-        <v>100.7381059448373</v>
+        <v>924.5682229973356</v>
       </c>
       <c r="E36" t="n">
-        <v>78.84709864997603</v>
+        <v>578.4347914600501</v>
       </c>
       <c r="F36" t="n">
-        <v>60.0226114399994</v>
+        <v>235.3678800076491</v>
       </c>
       <c r="G36" t="n">
-        <v>55.98259997866058</v>
+        <v>55.98259997866057</v>
       </c>
       <c r="H36" t="n">
         <v>51.92</v>
@@ -7028,31 +7028,31 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q36" t="n">
-        <v>2164.764564500508</v>
+        <v>2244.187340368535</v>
       </c>
       <c r="R36" t="n">
-        <v>1982.60944240224</v>
+        <v>2062.032218270268</v>
       </c>
       <c r="S36" t="n">
-        <v>1849.457698584356</v>
+        <v>1928.880474452383</v>
       </c>
       <c r="T36" t="n">
-        <v>1767.260375227614</v>
+        <v>1846.683151095642</v>
       </c>
       <c r="U36" t="n">
-        <v>1687.299081778216</v>
+        <v>1766.721857646244</v>
       </c>
       <c r="V36" t="n">
-        <v>1268.601438150418</v>
+        <v>1672.26663826087</v>
       </c>
       <c r="W36" t="n">
-        <v>1060.180821299454</v>
+        <v>1559.768514109528</v>
       </c>
       <c r="X36" t="n">
-        <v>960.3194683243149</v>
+        <v>1135.664736891965</v>
       </c>
       <c r="Y36" t="n">
-        <v>881.1362433080176</v>
+        <v>1056.481511875667</v>
       </c>
     </row>
     <row r="37">
@@ -7071,46 +7071,46 @@
         <v>769.5452468458327</v>
       </c>
       <c r="E37" t="n">
-        <v>809.1641510572457</v>
+        <v>809.1641510572764</v>
       </c>
       <c r="F37" t="n">
-        <v>855.3151236491811</v>
+        <v>855.3151236492118</v>
       </c>
       <c r="G37" t="n">
-        <v>931.1258141262304</v>
+        <v>931.125814126261</v>
       </c>
       <c r="H37" t="n">
-        <v>1027.892525187267</v>
+        <v>1027.892525187298</v>
       </c>
       <c r="I37" t="n">
-        <v>1189.283805434826</v>
+        <v>1189.283805434856</v>
       </c>
       <c r="J37" t="n">
-        <v>1515.576154611867</v>
+        <v>1515.576154611898</v>
       </c>
       <c r="K37" t="n">
-        <v>1619.080700024145</v>
+        <v>1619.080700024176</v>
       </c>
       <c r="L37" t="n">
-        <v>1608.654647405756</v>
+        <v>1608.654647405787</v>
       </c>
       <c r="M37" t="n">
-        <v>1505.227982468588</v>
+        <v>1505.227982468619</v>
       </c>
       <c r="N37" t="n">
-        <v>1348.401726605486</v>
+        <v>1348.401726605517</v>
       </c>
       <c r="O37" t="n">
-        <v>1114.295626111697</v>
+        <v>1114.295626111728</v>
       </c>
       <c r="P37" t="n">
-        <v>819.9299076645211</v>
+        <v>819.9299076645522</v>
       </c>
       <c r="Q37" t="n">
-        <v>463.4700425881595</v>
+        <v>463.4700425881906</v>
       </c>
       <c r="R37" t="n">
-        <v>81.94485949741244</v>
+        <v>81.94485949744347</v>
       </c>
       <c r="S37" t="n">
         <v>51.92</v>
@@ -7153,7 +7153,7 @@
         <v>292.4361325821661</v>
       </c>
       <c r="F38" t="n">
-        <v>207.6991338872046</v>
+        <v>207.6991338872047</v>
       </c>
       <c r="G38" t="n">
         <v>125.5027119537179</v>
@@ -7168,13 +7168,13 @@
         <v>133.4268380887174</v>
       </c>
       <c r="K38" t="n">
-        <v>775.9368380887173</v>
+        <v>366.8129733061596</v>
       </c>
       <c r="L38" t="n">
-        <v>1418.446838088717</v>
+        <v>1009.32297330616</v>
       </c>
       <c r="M38" t="n">
-        <v>1651.83297330616</v>
+        <v>1009.32297330616</v>
       </c>
       <c r="N38" t="n">
         <v>1651.83297330616</v>
@@ -7220,22 +7220,22 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1141.180125483445</v>
+        <v>668.0405455662462</v>
       </c>
       <c r="C39" t="n">
-        <v>776.43273917484</v>
+        <v>627.5355835000652</v>
       </c>
       <c r="D39" t="n">
-        <v>424.9805301872616</v>
+        <v>276.0833745124867</v>
       </c>
       <c r="E39" t="n">
-        <v>403.0895228924003</v>
+        <v>78.84709864997603</v>
       </c>
       <c r="F39" t="n">
-        <v>60.02261143999941</v>
+        <v>60.0226114399994</v>
       </c>
       <c r="G39" t="n">
-        <v>55.98259997866057</v>
+        <v>55.98259997866058</v>
       </c>
       <c r="H39" t="n">
         <v>51.92</v>
@@ -7274,7 +7274,7 @@
         <v>1928.880474452383</v>
       </c>
       <c r="T39" t="n">
-        <v>1846.683151095642</v>
+        <v>1846.683151095641</v>
       </c>
       <c r="U39" t="n">
         <v>1766.721857646244</v>
@@ -7286,10 +7286,10 @@
         <v>1559.768514109528</v>
       </c>
       <c r="X39" t="n">
-        <v>1459.907161134389</v>
+        <v>1135.664736891964</v>
       </c>
       <c r="Y39" t="n">
-        <v>1380.723936118092</v>
+        <v>1056.481511875667</v>
       </c>
     </row>
     <row r="40">
@@ -7320,34 +7320,34 @@
         <v>1027.892525187267</v>
       </c>
       <c r="I40" t="n">
-        <v>1189.283805434826</v>
+        <v>1189.283805434863</v>
       </c>
       <c r="J40" t="n">
-        <v>1515.576154611867</v>
+        <v>1515.576154611905</v>
       </c>
       <c r="K40" t="n">
-        <v>1619.080700024145</v>
+        <v>1619.080700024183</v>
       </c>
       <c r="L40" t="n">
-        <v>1608.654647405756</v>
+        <v>1608.654647405794</v>
       </c>
       <c r="M40" t="n">
-        <v>1505.227982468588</v>
+        <v>1505.227982468626</v>
       </c>
       <c r="N40" t="n">
-        <v>1348.401726605486</v>
+        <v>1348.401726605523</v>
       </c>
       <c r="O40" t="n">
-        <v>1114.295626111697</v>
+        <v>1114.295626111734</v>
       </c>
       <c r="P40" t="n">
-        <v>819.9299076645212</v>
+        <v>819.9299076645589</v>
       </c>
       <c r="Q40" t="n">
-        <v>463.4700425881596</v>
+        <v>463.4700425881972</v>
       </c>
       <c r="R40" t="n">
-        <v>81.94485949741255</v>
+        <v>81.94485949745018</v>
       </c>
       <c r="S40" t="n">
         <v>51.92</v>
@@ -7378,76 +7378,76 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>596.6553483293503</v>
+        <v>597.1205880922939</v>
       </c>
       <c r="C41" t="n">
-        <v>466.8830470738009</v>
+        <v>467.3482868367445</v>
       </c>
       <c r="D41" t="n">
-        <v>376.6414756194072</v>
+        <v>377.1067153823507</v>
       </c>
       <c r="E41" t="n">
-        <v>292.4361325821661</v>
+        <v>292.9013723451097</v>
       </c>
       <c r="F41" t="n">
-        <v>207.6991338872046</v>
+        <v>208.1643736501482</v>
       </c>
       <c r="G41" t="n">
-        <v>125.5027119537179</v>
+        <v>125.9679517166614</v>
       </c>
       <c r="H41" t="n">
-        <v>51.92</v>
+        <v>52.38523976294358</v>
       </c>
       <c r="I41" t="n">
         <v>51.92</v>
       </c>
       <c r="J41" t="n">
-        <v>559.4285273090126</v>
+        <v>133.4268380887174</v>
       </c>
       <c r="K41" t="n">
-        <v>933.7979500743317</v>
+        <v>307.5796384907274</v>
       </c>
       <c r="L41" t="n">
-        <v>1149.849898617045</v>
+        <v>523.631587033441</v>
       </c>
       <c r="M41" t="n">
-        <v>1792.359898617045</v>
+        <v>1166.141587033441</v>
       </c>
       <c r="N41" t="n">
-        <v>1792.359898617045</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="O41" t="n">
-        <v>1953.49</v>
+        <v>1812.963074689115</v>
       </c>
       <c r="P41" t="n">
-        <v>2596</v>
+        <v>2009.555081027735</v>
       </c>
       <c r="Q41" t="n">
         <v>2596</v>
       </c>
       <c r="R41" t="n">
-        <v>2595.534760237057</v>
+        <v>2596</v>
       </c>
       <c r="S41" t="n">
-        <v>2451.762030971221</v>
+        <v>2452.227270734164</v>
       </c>
       <c r="T41" t="n">
-        <v>2189.517714621877</v>
+        <v>2189.982954384821</v>
       </c>
       <c r="U41" t="n">
-        <v>1858.092802114017</v>
+        <v>1858.558041876961</v>
       </c>
       <c r="V41" t="n">
-        <v>1546.122070632377</v>
+        <v>1546.58731039532</v>
       </c>
       <c r="W41" t="n">
-        <v>1225.542801964753</v>
+        <v>1226.008041727697</v>
       </c>
       <c r="X41" t="n">
-        <v>951.5207479640785</v>
+        <v>951.9859877270221</v>
       </c>
       <c r="Y41" t="n">
-        <v>759.2809169713448</v>
+        <v>759.7461567342884</v>
       </c>
     </row>
     <row r="42">
@@ -7457,25 +7457,25 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1141.180125483445</v>
+        <v>343.7981213238224</v>
       </c>
       <c r="C42" t="n">
-        <v>776.43273917484</v>
+        <v>303.2931592576413</v>
       </c>
       <c r="D42" t="n">
-        <v>424.9805301872616</v>
+        <v>276.0833745124871</v>
       </c>
       <c r="E42" t="n">
-        <v>403.0895228924003</v>
+        <v>254.1923672176258</v>
       </c>
       <c r="F42" t="n">
-        <v>60.02261143999941</v>
+        <v>235.3678800076492</v>
       </c>
       <c r="G42" t="n">
-        <v>55.98259997866057</v>
+        <v>231.3278685463104</v>
       </c>
       <c r="H42" t="n">
-        <v>51.92</v>
+        <v>227.2652685676498</v>
       </c>
       <c r="I42" t="n">
         <v>51.92</v>
@@ -7505,28 +7505,28 @@
         <v>2244.187340368535</v>
       </c>
       <c r="R42" t="n">
-        <v>1886.686949702618</v>
+        <v>1737.789794027844</v>
       </c>
       <c r="S42" t="n">
-        <v>1753.535205884734</v>
+        <v>1280.395625967535</v>
       </c>
       <c r="T42" t="n">
-        <v>1671.337882527992</v>
+        <v>873.9558783683688</v>
       </c>
       <c r="U42" t="n">
-        <v>1591.376589078594</v>
+        <v>793.9945849189711</v>
       </c>
       <c r="V42" t="n">
-        <v>1496.92136969322</v>
+        <v>699.5393655335972</v>
       </c>
       <c r="W42" t="n">
-        <v>1384.423245541878</v>
+        <v>587.0412413822553</v>
       </c>
       <c r="X42" t="n">
-        <v>1284.561892566739</v>
+        <v>487.1798884071163</v>
       </c>
       <c r="Y42" t="n">
-        <v>1205.378667550442</v>
+        <v>407.996663390819</v>
       </c>
     </row>
     <row r="43">
@@ -7569,22 +7569,22 @@
         <v>1608.654647405756</v>
       </c>
       <c r="M43" t="n">
-        <v>1505.227982468588</v>
+        <v>1506.07469544798</v>
       </c>
       <c r="N43" t="n">
-        <v>1348.401726605486</v>
+        <v>1349.248439584877</v>
       </c>
       <c r="O43" t="n">
-        <v>1114.295626111697</v>
+        <v>1115.142339091088</v>
       </c>
       <c r="P43" t="n">
-        <v>819.9299076645212</v>
+        <v>820.7766206439126</v>
       </c>
       <c r="Q43" t="n">
-        <v>463.4700425881596</v>
+        <v>464.3167555675509</v>
       </c>
       <c r="R43" t="n">
-        <v>81.94485949741255</v>
+        <v>82.79157247680381</v>
       </c>
       <c r="S43" t="n">
         <v>51.92</v>
@@ -7615,40 +7615,40 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>597.1205880922942</v>
+        <v>597.1205880922939</v>
       </c>
       <c r="C44" t="n">
-        <v>467.3482868367447</v>
+        <v>467.3482868367445</v>
       </c>
       <c r="D44" t="n">
-        <v>377.106715382351</v>
+        <v>377.1067153823507</v>
       </c>
       <c r="E44" t="n">
-        <v>292.9013723451099</v>
+        <v>292.9013723451097</v>
       </c>
       <c r="F44" t="n">
-        <v>208.1643736501484</v>
+        <v>208.1643736501482</v>
       </c>
       <c r="G44" t="n">
-        <v>125.9679517166617</v>
+        <v>125.9679517166614</v>
       </c>
       <c r="H44" t="n">
-        <v>52.3852397629438</v>
+        <v>51.92</v>
       </c>
       <c r="I44" t="n">
         <v>51.92</v>
       </c>
       <c r="J44" t="n">
-        <v>559.4285273090126</v>
+        <v>133.4268380887174</v>
       </c>
       <c r="K44" t="n">
-        <v>1201.938527309012</v>
+        <v>775.9368380887173</v>
       </c>
       <c r="L44" t="n">
-        <v>1844.448527309012</v>
+        <v>1418.446838088717</v>
       </c>
       <c r="M44" t="n">
-        <v>2238.277892278425</v>
+        <v>2060.956838088718</v>
       </c>
       <c r="N44" t="n">
         <v>2238.277892278425</v>
@@ -7675,16 +7675,16 @@
         <v>1858.558041876961</v>
       </c>
       <c r="V44" t="n">
-        <v>1546.587310395321</v>
+        <v>1546.58731039532</v>
       </c>
       <c r="W44" t="n">
         <v>1226.008041727697</v>
       </c>
       <c r="X44" t="n">
-        <v>951.9859877270223</v>
+        <v>951.9859877270221</v>
       </c>
       <c r="Y44" t="n">
-        <v>759.7461567342887</v>
+        <v>759.7461567342884</v>
       </c>
     </row>
     <row r="45">
@@ -7694,25 +7694,25 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>816.9377012410212</v>
+        <v>686.2820590119659</v>
       </c>
       <c r="C45" t="n">
-        <v>452.1903149324157</v>
+        <v>321.5346727033605</v>
       </c>
       <c r="D45" t="n">
-        <v>100.7381059448373</v>
+        <v>294.3248879582063</v>
       </c>
       <c r="E45" t="n">
-        <v>78.84709864997603</v>
+        <v>272.4338806633451</v>
       </c>
       <c r="F45" t="n">
-        <v>60.0226114399994</v>
+        <v>253.6093934533685</v>
       </c>
       <c r="G45" t="n">
-        <v>55.98259997866058</v>
+        <v>249.5693819920296</v>
       </c>
       <c r="H45" t="n">
-        <v>51.92</v>
+        <v>245.506782013369</v>
       </c>
       <c r="I45" t="n">
         <v>51.92</v>
@@ -7742,28 +7742,28 @@
         <v>2244.187340368535</v>
       </c>
       <c r="R45" t="n">
-        <v>2062.032218270268</v>
+        <v>1756.031307473563</v>
       </c>
       <c r="S45" t="n">
-        <v>1928.880474452383</v>
+        <v>1622.879563655678</v>
       </c>
       <c r="T45" t="n">
-        <v>1671.337882527992</v>
+        <v>1540.682240298937</v>
       </c>
       <c r="U45" t="n">
-        <v>1591.376589078594</v>
+        <v>1460.720946849539</v>
       </c>
       <c r="V45" t="n">
-        <v>1496.92136969322</v>
+        <v>1366.265727464165</v>
       </c>
       <c r="W45" t="n">
-        <v>1384.423245541878</v>
+        <v>1253.767603312823</v>
       </c>
       <c r="X45" t="n">
-        <v>1284.561892566739</v>
+        <v>1153.906250337684</v>
       </c>
       <c r="Y45" t="n">
-        <v>1205.378667550442</v>
+        <v>1074.723025321387</v>
       </c>
     </row>
     <row r="46">
@@ -7815,10 +7815,10 @@
         <v>1114.295626111697</v>
       </c>
       <c r="P46" t="n">
-        <v>819.9299076645211</v>
+        <v>819.9299076645212</v>
       </c>
       <c r="Q46" t="n">
-        <v>464.3167555675508</v>
+        <v>463.4700425881596</v>
       </c>
       <c r="R46" t="n">
         <v>82.79157247680381</v>
@@ -7964,28 +7964,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>374.2405037325275</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>321.8400703517588</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>235.5012052109776</v>
       </c>
       <c r="M2" t="n">
-        <v>844.554996989051</v>
+        <v>846.2608914614127</v>
       </c>
       <c r="N2" t="n">
-        <v>776.3653500296342</v>
+        <v>404.0826666125488</v>
       </c>
       <c r="O2" t="n">
-        <v>181.0387865781018</v>
+        <v>1.159015302735668</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>501.1077446289929</v>
+        <v>128.5418702571336</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8043,7 +8043,7 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J3" t="n">
-        <v>223.7070799393687</v>
+        <v>227.4647419277884</v>
       </c>
       <c r="K3" t="n">
         <v>295.8802408630135</v>
@@ -8201,28 +8201,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>0.2405037325275146</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>321.8400703517588</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>309.2909949748743</v>
       </c>
       <c r="M5" t="n">
-        <v>471.5549969890509</v>
+        <v>472.2608914614128</v>
       </c>
       <c r="N5" t="n">
-        <v>644.138833103312</v>
+        <v>778.0826666125488</v>
       </c>
       <c r="O5" t="n">
-        <v>374.4816735941929</v>
+        <v>1.159015302735668</v>
       </c>
       <c r="P5" t="n">
-        <v>314.7432258698271</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>502.1077446289929</v>
+        <v>428.7520804932368</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8438,28 +8438,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>0.2405037325275146</v>
       </c>
       <c r="K8" t="n">
-        <v>321.3286984924623</v>
+        <v>321.8400703517588</v>
       </c>
       <c r="L8" t="n">
-        <v>308.6565929648241</v>
+        <v>309.2909949748743</v>
       </c>
       <c r="M8" t="n">
-        <v>771.0864144752693</v>
+        <v>472.2608914614128</v>
       </c>
       <c r="N8" t="n">
-        <v>777.3653500296342</v>
+        <v>704.2928768486519</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4816735941929551</v>
+        <v>1.159015302735668</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>128.1077446289929</v>
+        <v>502.5418702571336</v>
       </c>
       <c r="R8" t="n">
         <v>294.54111633436</v>
@@ -8678,10 +8678,10 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>473.08808040201</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>378.150932086181</v>
       </c>
       <c r="M11" t="n">
         <v>301.434429149855</v>
@@ -8690,13 +8690,13 @@
         <v>230.4920535472222</v>
       </c>
       <c r="O11" t="n">
-        <v>258.8704074657004</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
         <v>450.422215819576</v>
       </c>
       <c r="Q11" t="n">
-        <v>615.8520732695737</v>
+        <v>23.48346824708341</v>
       </c>
       <c r="R11" t="n">
         <v>294.54111633436</v>
@@ -8918,19 +8918,19 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>60.29262328527625</v>
+        <v>258.8704074657004</v>
       </c>
       <c r="M14" t="n">
         <v>301.434429149855</v>
       </c>
       <c r="N14" t="n">
-        <v>879.4920535472222</v>
+        <v>230.4920535472222</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>450.422215819576</v>
       </c>
       <c r="Q14" t="n">
         <v>615.8520732695737</v>
@@ -9149,19 +9149,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J17" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>60.29262328527625</v>
+        <v>473.0880804020101</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>430.7657085427136</v>
       </c>
       <c r="M17" t="n">
-        <v>301.434429149855</v>
+        <v>950.4344291498551</v>
       </c>
       <c r="N17" t="n">
-        <v>879.4920535472222</v>
+        <v>409.6042294964216</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -9170,7 +9170,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>615.8520732695737</v>
+        <v>23.48346824708341</v>
       </c>
       <c r="R17" t="n">
         <v>294.54111633436</v>
@@ -9389,7 +9389,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>3.200256351209731</v>
+        <v>473.0880804020101</v>
       </c>
       <c r="L20" t="n">
         <v>430.7657085427136</v>
@@ -9398,7 +9398,7 @@
         <v>950.4344291498551</v>
       </c>
       <c r="N20" t="n">
-        <v>879.4920535472222</v>
+        <v>409.6042294964216</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -9626,25 +9626,25 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>59.83165132871943</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>430.7657085427136</v>
       </c>
       <c r="M23" t="n">
-        <v>933.9781782242026</v>
+        <v>950.4344291498551</v>
       </c>
       <c r="N23" t="n">
-        <v>879.4920535472222</v>
+        <v>230.4920535472222</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>450.422215819576</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>23.48346824708341</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R23" t="n">
         <v>294.54111633436</v>
@@ -9860,19 +9860,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K26" t="n">
-        <v>473.0880804020101</v>
+        <v>473.08808040201</v>
       </c>
       <c r="L26" t="n">
         <v>430.7657085427136</v>
       </c>
       <c r="M26" t="n">
-        <v>480.5466050990546</v>
+        <v>699.241868512898</v>
       </c>
       <c r="N26" t="n">
-        <v>879.4920535472222</v>
+        <v>230.4920535472222</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -10097,10 +10097,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J29" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>3.661228307766578</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -10109,7 +10109,7 @@
         <v>950.4344291498551</v>
       </c>
       <c r="N29" t="n">
-        <v>879.4920535472222</v>
+        <v>721.0894134186553</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -10118,7 +10118,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>23.48346824708341</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R29" t="n">
         <v>294.54111633436</v>
@@ -10334,16 +10334,16 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K32" t="n">
-        <v>473.0880804020101</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>430.7657085427136</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>480.5466050990546</v>
+        <v>950.4344291498551</v>
       </c>
       <c r="N32" t="n">
         <v>879.4920535472222</v>
@@ -10355,7 +10355,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>23.48346824708341</v>
+        <v>27.14469655484982</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10571,13 +10571,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K35" t="n">
-        <v>473.0880804020101</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>17.50927946942295</v>
+        <v>60.29262328527625</v>
       </c>
       <c r="M35" t="n">
         <v>301.434429149855</v>
@@ -10811,16 +10811,16 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>473.0880804020101</v>
+        <v>59.83165132871943</v>
       </c>
       <c r="L38" t="n">
         <v>430.7657085427136</v>
       </c>
       <c r="M38" t="n">
-        <v>537.1780000765643</v>
+        <v>301.434429149855</v>
       </c>
       <c r="N38" t="n">
-        <v>230.4920535472222</v>
+        <v>879.4920535472222</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -11045,10 +11045,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J41" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>202.239012488191</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -11057,16 +11057,16 @@
         <v>950.4344291498551</v>
       </c>
       <c r="N41" t="n">
-        <v>230.4920535472222</v>
+        <v>721.0894134186553</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>450.422215819576</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>23.48346824708341</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R41" t="n">
         <v>294.54111633436</v>
@@ -11282,19 +11282,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J44" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>473.08808040201</v>
+        <v>473.0880804020101</v>
       </c>
       <c r="L44" t="n">
         <v>430.7657085427136</v>
       </c>
       <c r="M44" t="n">
-        <v>699.241868512898</v>
+        <v>950.4344291498551</v>
       </c>
       <c r="N44" t="n">
-        <v>230.4920535472222</v>
+        <v>409.6042294964216</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -22527,7 +22527,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>1.927393539210024</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -23411,7 +23411,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0.8382458495976817</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -23423,7 +23423,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>0.8382458495974561</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -24122,7 +24122,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>0.8382458495976817</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -24143,7 +24143,7 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.8382458495974596</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -24596,7 +24596,7 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0.8382458495976817</v>
+        <v>0.8382458495976959</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -24842,13 +24842,13 @@
         <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>0.8382458495974561</v>
       </c>
       <c r="P31" t="n">
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.8382458495973424</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -25328,7 +25328,7 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>0.8382458495974596</v>
+        <v>0.8382458495667287</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -25565,7 +25565,7 @@
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>0.8382458495973424</v>
+        <v>0.8382458495600922</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -25784,7 +25784,7 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>0.8382458495977119</v>
       </c>
       <c r="N43" t="n">
         <v>0</v>
@@ -25802,7 +25802,7 @@
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>0.8382458495973424</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -26033,10 +26033,10 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.8382458495974561</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>0.8382458495973424</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -26086,7 +26086,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>765967.6997732542</v>
+        <v>766241.2270214068</v>
       </c>
     </row>
     <row r="3">
@@ -26094,7 +26094,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1458731.836415187</v>
+        <v>1458898.599204333</v>
       </c>
     </row>
     <row r="4">
@@ -26102,7 +26102,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2151389.208598115</v>
+        <v>2151555.971387261</v>
       </c>
     </row>
     <row r="5">
@@ -26110,7 +26110,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2843683.574435828</v>
+        <v>2843767.955724974</v>
       </c>
     </row>
     <row r="6">
@@ -26118,7 +26118,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>3536329.881773541</v>
+        <v>3536414.263062687</v>
       </c>
     </row>
     <row r="7">
@@ -26126,7 +26126,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4228976.189111253</v>
+        <v>4229060.570400399</v>
       </c>
     </row>
     <row r="8">
@@ -26134,7 +26134,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4921622.496448962</v>
+        <v>4921706.877738109</v>
       </c>
     </row>
     <row r="9">
@@ -26142,7 +26142,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5614268.803786672</v>
+        <v>5614353.185075818</v>
       </c>
     </row>
     <row r="10">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6306915.111124381</v>
+        <v>6306999.492413527</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6999561.41846209</v>
+        <v>6999645.799751237</v>
       </c>
     </row>
     <row r="12">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7692207.725799805</v>
+        <v>7692292.107088952</v>
       </c>
     </row>
     <row r="13">
@@ -26174,7 +26174,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>8384854.033137524</v>
+        <v>8384938.414426669</v>
       </c>
     </row>
     <row r="14">
@@ -26182,7 +26182,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>9077500.340475243</v>
+        <v>9077584.721764388</v>
       </c>
     </row>
     <row r="15">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>9770146.647812959</v>
+        <v>9770231.029102106</v>
       </c>
     </row>
     <row r="16">
@@ -26198,7 +26198,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>10462792.95515068</v>
+        <v>10462877.33643982</v>
       </c>
     </row>
   </sheetData>
@@ -26269,13 +26269,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1511068.343768248</v>
+        <v>1511252.448399114</v>
       </c>
       <c r="C2" t="n">
         <v>1511252.448399114</v>
       </c>
       <c r="D2" t="n">
-        <v>1511252.448399113</v>
+        <v>1511252.448399114</v>
       </c>
       <c r="E2" t="n">
         <v>1511228.306918646</v>
@@ -26293,25 +26293,25 @@
         <v>1511228.306918645</v>
       </c>
       <c r="J2" t="n">
-        <v>1511228.306918646</v>
+        <v>1511228.306918645</v>
       </c>
       <c r="K2" t="n">
         <v>1511228.306918646</v>
       </c>
       <c r="L2" t="n">
-        <v>1511228.306918646</v>
+        <v>1511228.306918645</v>
       </c>
       <c r="M2" t="n">
         <v>1511228.306918646</v>
       </c>
       <c r="N2" t="n">
+        <v>1511228.306918647</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1511228.306918646</v>
+      </c>
+      <c r="P2" t="n">
         <v>1511228.306918645</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1511228.306918645</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1511228.306918646</v>
       </c>
     </row>
     <row r="3">
@@ -26321,16 +26321,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>231721</v>
+        <v>231098</v>
       </c>
       <c r="C3" t="n">
-        <v>352</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>588575</v>
+        <v>589550</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -26345,10 +26345,10 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>388096</v>
+        <v>388448</v>
       </c>
       <c r="K3" t="n">
-        <v>352</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>577307.7597977305</v>
+        <v>570963.5697337884</v>
       </c>
       <c r="C4" t="n">
-        <v>575232.1895180242</v>
+        <v>568954.6475462997</v>
       </c>
       <c r="D4" t="n">
-        <v>573221.1009892204</v>
+        <v>566943.0001304757</v>
       </c>
       <c r="E4" t="n">
-        <v>489938.979796175</v>
+        <v>483475.9886658208</v>
       </c>
       <c r="F4" t="n">
-        <v>488252.9169779522</v>
+        <v>481789.9258475979</v>
       </c>
       <c r="G4" t="n">
-        <v>486564.5274562991</v>
+        <v>480101.5363259449</v>
       </c>
       <c r="H4" t="n">
-        <v>484873.7945463364</v>
+        <v>478410.8034159822</v>
       </c>
       <c r="I4" t="n">
-        <v>483180.7013457892</v>
+        <v>476717.7102154349</v>
       </c>
       <c r="J4" t="n">
-        <v>481485.2307308645</v>
+        <v>475022.2396005102</v>
       </c>
       <c r="K4" t="n">
-        <v>479787.365352031</v>
+        <v>473324.3742216767</v>
       </c>
       <c r="L4" t="n">
-        <v>478087.087629687</v>
+        <v>471624.0964993328</v>
       </c>
       <c r="M4" t="n">
-        <v>476384.3797497193</v>
+        <v>469921.3886193655</v>
       </c>
       <c r="N4" t="n">
-        <v>474679.2236589554</v>
+        <v>468216.2325286018</v>
       </c>
       <c r="O4" t="n">
-        <v>472971.6010604933</v>
+        <v>466508.609930139</v>
       </c>
       <c r="P4" t="n">
-        <v>471261.4934089098</v>
+        <v>464798.5022785557</v>
       </c>
     </row>
     <row r="5">
@@ -26425,13 +26425,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>58551.39999999999</v>
+        <v>58590.39999999999</v>
       </c>
       <c r="C5" t="n">
-        <v>58612.2</v>
+        <v>58590.39999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>58612.2</v>
+        <v>58590.39999999999</v>
       </c>
       <c r="E5" t="n">
         <v>73944.549</v>
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>643488.1839705176</v>
+        <v>650600.4786653256</v>
       </c>
       <c r="C6" t="n">
-        <v>877056.0588810896</v>
+        <v>883707.4008528142</v>
       </c>
       <c r="D6" t="n">
-        <v>879419.1474098931</v>
+        <v>885719.0482686384</v>
       </c>
       <c r="E6" t="n">
-        <v>358769.7781224705</v>
+        <v>364257.7692528252</v>
       </c>
       <c r="F6" t="n">
-        <v>949030.840940694</v>
+        <v>955493.8320710481</v>
       </c>
       <c r="G6" t="n">
-        <v>950719.2304623463</v>
+        <v>957182.2215927009</v>
       </c>
       <c r="H6" t="n">
-        <v>952409.9633723093</v>
+        <v>958872.954502664</v>
       </c>
       <c r="I6" t="n">
-        <v>954103.0565728553</v>
+        <v>960566.0477032104</v>
       </c>
       <c r="J6" t="n">
-        <v>567702.5271877815</v>
+        <v>573813.5183181351</v>
       </c>
       <c r="K6" t="n">
-        <v>957144.3925666148</v>
+        <v>963959.3836969692</v>
       </c>
       <c r="L6" t="n">
-        <v>959196.6702889587</v>
+        <v>965659.6614193125</v>
       </c>
       <c r="M6" t="n">
-        <v>864099.3781689267</v>
+        <v>870562.3692992809</v>
       </c>
       <c r="N6" t="n">
-        <v>962604.5342596899</v>
+        <v>969067.5253900454</v>
       </c>
       <c r="O6" t="n">
-        <v>707512.1568581518</v>
+        <v>713975.1479885065</v>
       </c>
       <c r="P6" t="n">
-        <v>966022.2645097362</v>
+        <v>972485.2556400896</v>
       </c>
     </row>
   </sheetData>
@@ -26807,13 +26807,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C3" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D3" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E3" t="n">
         <v>344</v>
@@ -26859,7 +26859,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C4" t="n">
         <v>374</v>
@@ -27014,7 +27014,7 @@
         <v>321</v>
       </c>
       <c r="P2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -27024,7 +27024,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C3" t="n">
         <v>-0</v>
@@ -27033,7 +27033,7 @@
         <v>-0</v>
       </c>
       <c r="E3" t="n">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F3" t="n">
         <v>-0</v>
@@ -27076,10 +27076,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>-0</v>
       </c>
       <c r="D4" t="n">
         <v>-0</v>
@@ -27100,10 +27100,10 @@
         <v>-0</v>
       </c>
       <c r="J4" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>-0</v>
       </c>
       <c r="L4" t="n">
         <v>-0</v>
@@ -27317,10 +27317,10 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -27454,7 +27454,7 @@
         <v>400</v>
       </c>
       <c r="I2" t="n">
-        <v>134.1177124465037</v>
+        <v>132.4740095033003</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -27481,7 +27481,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>224.8682520946245</v>
+        <v>225.120779732817</v>
       </c>
       <c r="S2" t="n">
         <v>400</v>
@@ -27512,10 +27512,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>384.5565566463266</v>
+        <v>35.56948498147727</v>
       </c>
       <c r="C3" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>347.9376868977026</v>
@@ -27530,10 +27530,10 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>330.0491815260438</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>209.5726123064429</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -27557,7 +27557,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>144.7989632036872</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>400</v>
@@ -27581,7 +27581,7 @@
         <v>400</v>
       </c>
       <c r="Y3" t="n">
-        <v>84.27235085884922</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="4">
@@ -27594,34 +27594,34 @@
         <v>287.1138003370787</v>
       </c>
       <c r="C4" t="n">
-        <v>272.7252466480447</v>
+        <v>334.7108319933212</v>
       </c>
       <c r="D4" t="n">
-        <v>285.5362180555555</v>
+        <v>400</v>
       </c>
       <c r="E4" t="n">
-        <v>280.9809048369565</v>
+        <v>400</v>
       </c>
       <c r="F4" t="n">
-        <v>274.3828559677419</v>
+        <v>400</v>
       </c>
       <c r="G4" t="n">
-        <v>244.858135136612</v>
+        <v>244.8599384153005</v>
       </c>
       <c r="H4" t="n">
-        <v>227.1197490524383</v>
+        <v>400</v>
       </c>
       <c r="I4" t="n">
-        <v>171.047816275856</v>
+        <v>400</v>
       </c>
       <c r="J4" t="n">
-        <v>395.1372930982029</v>
+        <v>396.2647849014816</v>
       </c>
       <c r="K4" t="n">
-        <v>266.941429538848</v>
+        <v>400</v>
       </c>
       <c r="L4" t="n">
-        <v>395.9334970102382</v>
+        <v>396.2015953708939</v>
       </c>
       <c r="M4" t="n">
         <v>400</v>
@@ -27642,25 +27642,25 @@
         <v>400</v>
       </c>
       <c r="S4" t="n">
-        <v>359.1365780635112</v>
+        <v>400</v>
       </c>
       <c r="T4" t="n">
-        <v>400</v>
+        <v>209.2386648669134</v>
       </c>
       <c r="U4" t="n">
-        <v>400</v>
+        <v>150.9483584875727</v>
       </c>
       <c r="V4" t="n">
-        <v>400</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W4" t="n">
-        <v>400</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X4" t="n">
-        <v>400</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y4" t="n">
-        <v>316.870828723006</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="5">
@@ -27688,40 +27688,40 @@
         <v>400</v>
       </c>
       <c r="H5" t="n">
+        <v>398.2013121321735</v>
+      </c>
+      <c r="I5" t="n">
+        <v>134.2726973711268</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>225.120779732817</v>
+      </c>
+      <c r="S5" t="n">
         <v>400</v>
-      </c>
-      <c r="I5" t="n">
-        <v>134.1177124465037</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>224.8682520946261</v>
-      </c>
-      <c r="S5" t="n">
-        <v>398.0465935392085</v>
       </c>
       <c r="T5" t="n">
         <v>400</v>
@@ -27749,28 +27749,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>384.5565566463266</v>
+        <v>10.55655664632661</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F6" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G6" t="n">
-        <v>325.517988705216</v>
+        <v>325.5201396486123</v>
       </c>
       <c r="H6" t="n">
-        <v>330.0284079411381</v>
+        <v>330.0491815260438</v>
       </c>
       <c r="I6" t="n">
-        <v>209.4985557026693</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -27794,7 +27794,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>144.7989632036872</v>
+        <v>145.073529241423</v>
       </c>
       <c r="R6" t="n">
         <v>400</v>
@@ -27815,10 +27815,10 @@
         <v>400</v>
       </c>
       <c r="X6" t="n">
-        <v>267.8628177939761</v>
+        <v>176.891959306039</v>
       </c>
       <c r="Y6" t="n">
-        <v>399.3913927661343</v>
+        <v>25.39139276613435</v>
       </c>
     </row>
     <row r="7">
@@ -27843,22 +27843,22 @@
         <v>274.3828559677419</v>
       </c>
       <c r="G7" t="n">
-        <v>244.858135136612</v>
+        <v>244.8599384153005</v>
       </c>
       <c r="H7" t="n">
-        <v>322.7835689333214</v>
+        <v>227.1357818393235</v>
       </c>
       <c r="I7" t="n">
         <v>400</v>
       </c>
       <c r="J7" t="n">
-        <v>396.1372930982029</v>
+        <v>396.2647849014816</v>
       </c>
       <c r="K7" t="n">
-        <v>266.941429538848</v>
+        <v>267.1509377355693</v>
       </c>
       <c r="L7" t="n">
-        <v>395.9334970102382</v>
+        <v>396.2015953708939</v>
       </c>
       <c r="M7" t="n">
         <v>400</v>
@@ -27879,13 +27879,13 @@
         <v>400</v>
       </c>
       <c r="S7" t="n">
-        <v>359.1365780635112</v>
+        <v>400</v>
       </c>
       <c r="T7" t="n">
-        <v>209.2309599488807</v>
+        <v>209.2386648669134</v>
       </c>
       <c r="U7" t="n">
-        <v>150.9482601269169</v>
+        <v>207.1237586900172</v>
       </c>
       <c r="V7" t="n">
         <v>199.1703102162162</v>
@@ -27910,7 +27910,7 @@
         <v>400</v>
       </c>
       <c r="C8" t="n">
-        <v>398.0465935392086</v>
+        <v>400</v>
       </c>
       <c r="D8" t="n">
         <v>400</v>
@@ -27928,7 +27928,7 @@
         <v>400</v>
       </c>
       <c r="I8" t="n">
-        <v>134.1177124465037</v>
+        <v>132.4740095033003</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -27955,7 +27955,7 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>224.8682520946261</v>
+        <v>225.120779732817</v>
       </c>
       <c r="S8" t="n">
         <v>400</v>
@@ -27989,25 +27989,25 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C9" t="n">
-        <v>207.4990601318526</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G9" t="n">
-        <v>325.517988705216</v>
+        <v>325.5201396486123</v>
       </c>
       <c r="H9" t="n">
-        <v>330.0284079411381</v>
+        <v>330.0491815260438</v>
       </c>
       <c r="I9" t="n">
-        <v>209.4985557026693</v>
+        <v>84.14540975930272</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -28031,7 +28031,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>144.7989632036872</v>
+        <v>145.073529241423</v>
       </c>
       <c r="R9" t="n">
         <v>400</v>
@@ -28046,13 +28046,13 @@
         <v>400</v>
       </c>
       <c r="V9" t="n">
-        <v>400</v>
+        <v>40.51066719152016</v>
       </c>
       <c r="W9" t="n">
-        <v>400</v>
+        <v>58.37314290982852</v>
       </c>
       <c r="X9" t="n">
-        <v>400</v>
+        <v>45.86273944538755</v>
       </c>
       <c r="Y9" t="n">
         <v>399.3913927661343</v>
@@ -28065,37 +28065,37 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>287.1138003370787</v>
+        <v>400</v>
       </c>
       <c r="C10" t="n">
-        <v>272.7252466480447</v>
+        <v>400</v>
       </c>
       <c r="D10" t="n">
-        <v>301.1766742504699</v>
+        <v>400</v>
       </c>
       <c r="E10" t="n">
-        <v>400</v>
+        <v>280.9809048369565</v>
       </c>
       <c r="F10" t="n">
-        <v>400</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G10" t="n">
-        <v>400</v>
+        <v>244.8599384153005</v>
       </c>
       <c r="H10" t="n">
-        <v>400</v>
+        <v>227.1357818393235</v>
       </c>
       <c r="I10" t="n">
-        <v>400</v>
+        <v>171.1020457840527</v>
       </c>
       <c r="J10" t="n">
-        <v>396.1372930982029</v>
+        <v>22.26478490148153</v>
       </c>
       <c r="K10" t="n">
-        <v>400</v>
+        <v>267.1509377355693</v>
       </c>
       <c r="L10" t="n">
-        <v>400</v>
+        <v>396.2015953708939</v>
       </c>
       <c r="M10" t="n">
         <v>400</v>
@@ -28116,25 +28116,25 @@
         <v>400</v>
       </c>
       <c r="S10" t="n">
+        <v>359.1680042930194</v>
+      </c>
+      <c r="T10" t="n">
+        <v>336.5432435627183</v>
+      </c>
+      <c r="U10" t="n">
         <v>400</v>
       </c>
-      <c r="T10" t="n">
-        <v>209.2309599488807</v>
-      </c>
-      <c r="U10" t="n">
-        <v>150.9482601269169</v>
-      </c>
       <c r="V10" t="n">
-        <v>199.1703102162162</v>
+        <v>400</v>
       </c>
       <c r="W10" t="n">
-        <v>226.3728098387097</v>
+        <v>400</v>
       </c>
       <c r="X10" t="n">
-        <v>247.4436454301076</v>
+        <v>400</v>
       </c>
       <c r="Y10" t="n">
-        <v>287.4653528494624</v>
+        <v>400</v>
       </c>
     </row>
     <row r="11">
@@ -28165,7 +28165,7 @@
         <v>321</v>
       </c>
       <c r="I11" t="n">
-        <v>96.76634561233286</v>
+        <v>96.3057582470185</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -28192,7 +28192,7 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>163.5485039252921</v>
+        <v>164.009091290606</v>
       </c>
       <c r="S11" t="n">
         <v>321</v>
@@ -28223,7 +28223,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>147.4081841180272</v>
+        <v>321</v>
       </c>
       <c r="C12" t="n">
         <v>321</v>
@@ -28235,16 +28235,16 @@
         <v>321</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G12" t="n">
         <v>321</v>
       </c>
       <c r="H12" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>191.6509141932353</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -28280,7 +28280,7 @@
         <v>321</v>
       </c>
       <c r="U12" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
         <v>321</v>
@@ -28289,10 +28289,10 @@
         <v>321</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>18.05909831126229</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
     </row>
     <row r="13">
@@ -28399,7 +28399,7 @@
         <v>321</v>
       </c>
       <c r="H14" t="n">
-        <v>321</v>
+        <v>320.5394126346856</v>
       </c>
       <c r="I14" t="n">
         <v>96.76634561233286</v>
@@ -28432,7 +28432,7 @@
         <v>164.009091290606</v>
       </c>
       <c r="S14" t="n">
-        <v>320.539412634686</v>
+        <v>321</v>
       </c>
       <c r="T14" t="n">
         <v>321</v>
@@ -28466,7 +28466,7 @@
         <v>321</v>
       </c>
       <c r="D15" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -28475,7 +28475,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>147.4081841180272</v>
       </c>
       <c r="H15" t="n">
         <v>321</v>
@@ -28529,7 +28529,7 @@
         <v>321</v>
       </c>
       <c r="Y15" t="n">
-        <v>147.4081841180273</v>
+        <v>321</v>
       </c>
     </row>
     <row r="16">
@@ -28630,7 +28630,7 @@
         <v>321</v>
       </c>
       <c r="F17" t="n">
-        <v>321</v>
+        <v>320.5394126346857</v>
       </c>
       <c r="G17" t="n">
         <v>321</v>
@@ -28639,7 +28639,7 @@
         <v>321</v>
       </c>
       <c r="I17" t="n">
-        <v>96.3057582470185</v>
+        <v>96.76634561233286</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -28937,16 +28937,16 @@
         <v>321</v>
       </c>
       <c r="C21" t="n">
-        <v>321</v>
+        <v>147.4081841180271</v>
       </c>
       <c r="D21" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
         <v>321</v>
@@ -28994,16 +28994,16 @@
         <v>321</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="Y21" t="n">
-        <v>147.4081841180271</v>
+        <v>321</v>
       </c>
     </row>
     <row r="22">
@@ -29104,7 +29104,7 @@
         <v>321</v>
       </c>
       <c r="F23" t="n">
-        <v>320.5394126346858</v>
+        <v>321</v>
       </c>
       <c r="G23" t="n">
         <v>321</v>
@@ -29113,7 +29113,7 @@
         <v>321</v>
       </c>
       <c r="I23" t="n">
-        <v>96.76634561233286</v>
+        <v>96.3057582470187</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -29171,10 +29171,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
         <v>321</v>
@@ -29225,22 +29225,22 @@
         <v>321</v>
       </c>
       <c r="T24" t="n">
-        <v>147.4081841180269</v>
+        <v>321</v>
       </c>
       <c r="U24" t="n">
         <v>321</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>147.4081841180267</v>
       </c>
       <c r="Y24" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -29350,7 +29350,7 @@
         <v>321</v>
       </c>
       <c r="I26" t="n">
-        <v>96.3057582470185</v>
+        <v>96.76634561233286</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -29377,7 +29377,7 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>164.009091290606</v>
+        <v>163.5485039252921</v>
       </c>
       <c r="S26" t="n">
         <v>321</v>
@@ -29408,7 +29408,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="C27" t="n">
         <v>321</v>
@@ -29429,7 +29429,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>191.6509141932353</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -29465,19 +29465,19 @@
         <v>321</v>
       </c>
       <c r="U27" t="n">
-        <v>321</v>
+        <v>147.4081841180269</v>
       </c>
       <c r="V27" t="n">
         <v>321</v>
       </c>
       <c r="W27" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="Y27" t="n">
-        <v>18.05909831126229</v>
+        <v>321</v>
       </c>
     </row>
     <row r="28">
@@ -29578,7 +29578,7 @@
         <v>321</v>
       </c>
       <c r="F29" t="n">
-        <v>320.5394126346858</v>
+        <v>321</v>
       </c>
       <c r="G29" t="n">
         <v>321</v>
@@ -29587,7 +29587,7 @@
         <v>321</v>
       </c>
       <c r="I29" t="n">
-        <v>96.76634561233286</v>
+        <v>96.3057582470185</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -29657,13 +29657,13 @@
         <v>321</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G30" t="n">
-        <v>147.4081841180266</v>
+        <v>321</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="I30" t="n">
         <v>191.6509141932353</v>
@@ -29702,19 +29702,19 @@
         <v>321</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="V30" t="n">
-        <v>321</v>
+        <v>147.4081841180271</v>
       </c>
       <c r="W30" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -29824,7 +29824,7 @@
         <v>321</v>
       </c>
       <c r="I32" t="n">
-        <v>96.3057582470187</v>
+        <v>96.76634561233286</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -29872,7 +29872,7 @@
         <v>321</v>
       </c>
       <c r="Y32" t="n">
-        <v>321</v>
+        <v>320.5394126346858</v>
       </c>
     </row>
     <row r="33">
@@ -29888,16 +29888,16 @@
         <v>321</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G33" t="n">
-        <v>321</v>
+        <v>147.4081841180267</v>
       </c>
       <c r="H33" t="n">
         <v>321</v>
@@ -29930,7 +29930,7 @@
         <v>78.62854810934749</v>
       </c>
       <c r="R33" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>321</v>
@@ -29945,10 +29945,10 @@
         <v>321</v>
       </c>
       <c r="W33" t="n">
-        <v>147.408184118027</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
         <v>321</v>
@@ -30061,7 +30061,7 @@
         <v>321</v>
       </c>
       <c r="I35" t="n">
-        <v>96.76634561233286</v>
+        <v>96.3057582470187</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -30088,7 +30088,7 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>163.5485039252921</v>
+        <v>164.009091290606</v>
       </c>
       <c r="S35" t="n">
         <v>321</v>
@@ -30119,22 +30119,22 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="D36" t="n">
         <v>321</v>
       </c>
       <c r="E36" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>321</v>
+        <v>147.4081841180268</v>
       </c>
       <c r="H36" t="n">
         <v>321</v>
@@ -30164,7 +30164,7 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R36" t="n">
         <v>321</v>
@@ -30179,13 +30179,13 @@
         <v>321</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="W36" t="n">
-        <v>226.0367322273741</v>
+        <v>321</v>
       </c>
       <c r="X36" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
         <v>321</v>
@@ -30207,7 +30207,7 @@
         <v>321</v>
       </c>
       <c r="E37" t="n">
-        <v>321</v>
+        <v>321.000000000031</v>
       </c>
       <c r="F37" t="n">
         <v>321</v>
@@ -30356,19 +30356,19 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>147.4081841180269</v>
+        <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>321</v>
+        <v>147.408184118027</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G39" t="n">
         <v>321</v>
@@ -30422,7 +30422,7 @@
         <v>321</v>
       </c>
       <c r="X39" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
         <v>321</v>
@@ -30456,7 +30456,7 @@
         <v>321</v>
       </c>
       <c r="I40" t="n">
-        <v>321</v>
+        <v>321.0000000000383</v>
       </c>
       <c r="J40" t="n">
         <v>321</v>
@@ -30535,7 +30535,7 @@
         <v>321</v>
       </c>
       <c r="I41" t="n">
-        <v>96.76634561233286</v>
+        <v>96.3057582470187</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -30562,7 +30562,7 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>163.5485039252921</v>
+        <v>164.009091290606</v>
       </c>
       <c r="S41" t="n">
         <v>321</v>
@@ -30596,16 +30596,16 @@
         <v>321</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E42" t="n">
         <v>321</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G42" t="n">
         <v>321</v>
@@ -30614,7 +30614,7 @@
         <v>321</v>
       </c>
       <c r="I42" t="n">
-        <v>191.6509141932353</v>
+        <v>18.05909831126205</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -30641,13 +30641,13 @@
         <v>78.62854810934749</v>
       </c>
       <c r="R42" t="n">
-        <v>147.408184118027</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
         <v>321</v>
@@ -30769,10 +30769,10 @@
         <v>321</v>
       </c>
       <c r="H44" t="n">
-        <v>321</v>
+        <v>320.5394126346858</v>
       </c>
       <c r="I44" t="n">
-        <v>96.3057582470185</v>
+        <v>96.76634561233286</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -30836,7 +30836,7 @@
         <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E45" t="n">
         <v>321</v>
@@ -30851,7 +30851,7 @@
         <v>321</v>
       </c>
       <c r="I45" t="n">
-        <v>191.6509141932353</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -30878,13 +30878,13 @@
         <v>78.62854810934749</v>
       </c>
       <c r="R45" t="n">
-        <v>321</v>
+        <v>18.05909831126201</v>
       </c>
       <c r="S45" t="n">
         <v>321</v>
       </c>
       <c r="T45" t="n">
-        <v>147.4081841180271</v>
+        <v>321</v>
       </c>
       <c r="U45" t="n">
         <v>321</v>
@@ -31091,49 +31091,49 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4140703517587936</v>
+        <v>0.4100502512562811</v>
       </c>
       <c r="H2" t="n">
-        <v>4.240597989949746</v>
+        <v>4.199427135678389</v>
       </c>
       <c r="I2" t="n">
-        <v>15.96344723618091</v>
+        <v>15.80846231155779</v>
       </c>
       <c r="J2" t="n">
-        <v>35.14370351758794</v>
+        <v>34.80250251256282</v>
       </c>
       <c r="K2" t="n">
-        <v>52.67130150753769</v>
+        <v>52.15992964824121</v>
       </c>
       <c r="L2" t="n">
-        <v>65.34340703517589</v>
+        <v>64.70900502512563</v>
       </c>
       <c r="M2" t="n">
-        <v>72.70713065326633</v>
+        <v>72.00123618090453</v>
       </c>
       <c r="N2" t="n">
-        <v>73.88360804020101</v>
+        <v>73.16629145728643</v>
       </c>
       <c r="O2" t="n">
-        <v>69.76619597989949</v>
+        <v>69.08885427135678</v>
       </c>
       <c r="P2" t="n">
-        <v>59.54383417085427</v>
+        <v>58.96573869346734</v>
       </c>
       <c r="Q2" t="n">
-        <v>44.71493969849246</v>
+        <v>44.28081407035176</v>
       </c>
       <c r="R2" t="n">
-        <v>26.01034673366835</v>
+        <v>25.75781909547739</v>
       </c>
       <c r="S2" t="n">
-        <v>9.435628140703519</v>
+        <v>9.344020100502515</v>
       </c>
       <c r="T2" t="n">
-        <v>1.81259296482412</v>
+        <v>1.794994974874371</v>
       </c>
       <c r="U2" t="n">
-        <v>0.03312562814070349</v>
+        <v>0.03280402010050248</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -31170,49 +31170,49 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2215471698113208</v>
+        <v>0.2193962264150943</v>
       </c>
       <c r="H3" t="n">
-        <v>2.139679245283019</v>
+        <v>2.118905660377359</v>
       </c>
       <c r="I3" t="n">
-        <v>7.627830188679247</v>
+        <v>7.553773584905661</v>
       </c>
       <c r="J3" t="n">
-        <v>20.93134905660378</v>
+        <v>20.7281320754717</v>
       </c>
       <c r="K3" t="n">
-        <v>35.77500943396227</v>
+        <v>35.42767924528302</v>
       </c>
       <c r="L3" t="n">
-        <v>48.10391509433963</v>
+        <v>47.63688679245283</v>
       </c>
       <c r="M3" t="n">
-        <v>56.13499999999999</v>
+        <v>55.58999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>57.62072641509435</v>
+        <v>57.06130188679246</v>
       </c>
       <c r="O3" t="n">
-        <v>52.71170754716981</v>
+        <v>52.19994339622642</v>
       </c>
       <c r="P3" t="n">
-        <v>42.3057924528302</v>
+        <v>41.89505660377359</v>
       </c>
       <c r="Q3" t="n">
-        <v>28.28030188679246</v>
+        <v>28.00573584905661</v>
       </c>
       <c r="R3" t="n">
-        <v>13.75535849056604</v>
+        <v>13.62181132075472</v>
       </c>
       <c r="S3" t="n">
-        <v>4.115141509433959</v>
+        <v>4.07518867924528</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8929905660377355</v>
+        <v>0.8843207547169808</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01457547169811321</v>
+        <v>0.01443396226415095</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -31249,49 +31249,49 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1857377049180328</v>
+        <v>0.1839344262295082</v>
       </c>
       <c r="H4" t="n">
-        <v>1.651377049180329</v>
+        <v>1.635344262295083</v>
       </c>
       <c r="I4" t="n">
-        <v>5.585639344262296</v>
+        <v>5.531409836065575</v>
       </c>
       <c r="J4" t="n">
-        <v>13.13165573770492</v>
+        <v>13.00416393442623</v>
       </c>
       <c r="K4" t="n">
-        <v>21.57934426229507</v>
+        <v>21.36983606557376</v>
       </c>
       <c r="L4" t="n">
-        <v>27.61413114754098</v>
+        <v>27.34603278688525</v>
       </c>
       <c r="M4" t="n">
-        <v>29.11522950819672</v>
+        <v>28.83255737704917</v>
       </c>
       <c r="N4" t="n">
-        <v>28.42293442622952</v>
+        <v>28.1469836065574</v>
       </c>
       <c r="O4" t="n">
-        <v>26.25318032786886</v>
+        <v>25.99829508196722</v>
       </c>
       <c r="P4" t="n">
-        <v>22.46413114754097</v>
+        <v>22.24603278688523</v>
       </c>
       <c r="Q4" t="n">
-        <v>15.553</v>
+        <v>15.402</v>
       </c>
       <c r="R4" t="n">
-        <v>8.351442622950817</v>
+        <v>8.270360655737703</v>
       </c>
       <c r="S4" t="n">
-        <v>3.236901639344261</v>
+        <v>3.205475409836064</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7936065573770489</v>
+        <v>0.785901639344262</v>
       </c>
       <c r="U4" t="n">
-        <v>0.01013114754098362</v>
+        <v>0.01003278688524591</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -31328,49 +31328,49 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4140703517587936</v>
+        <v>0.4100502512562811</v>
       </c>
       <c r="H5" t="n">
-        <v>4.240597989949746</v>
+        <v>4.199427135678389</v>
       </c>
       <c r="I5" t="n">
-        <v>15.96344723618091</v>
+        <v>15.80846231155779</v>
       </c>
       <c r="J5" t="n">
-        <v>35.14370351758794</v>
+        <v>34.80250251256282</v>
       </c>
       <c r="K5" t="n">
-        <v>52.67130150753769</v>
+        <v>52.15992964824121</v>
       </c>
       <c r="L5" t="n">
-        <v>65.34340703517589</v>
+        <v>64.70900502512563</v>
       </c>
       <c r="M5" t="n">
-        <v>72.70713065326633</v>
+        <v>72.00123618090453</v>
       </c>
       <c r="N5" t="n">
-        <v>73.88360804020101</v>
+        <v>73.16629145728643</v>
       </c>
       <c r="O5" t="n">
-        <v>69.76619597989949</v>
+        <v>69.08885427135678</v>
       </c>
       <c r="P5" t="n">
-        <v>59.54383417085427</v>
+        <v>58.96573869346734</v>
       </c>
       <c r="Q5" t="n">
-        <v>44.71493969849246</v>
+        <v>44.28081407035176</v>
       </c>
       <c r="R5" t="n">
-        <v>26.01034673366835</v>
+        <v>25.75781909547739</v>
       </c>
       <c r="S5" t="n">
-        <v>9.435628140703519</v>
+        <v>9.344020100502515</v>
       </c>
       <c r="T5" t="n">
-        <v>1.81259296482412</v>
+        <v>1.794994974874371</v>
       </c>
       <c r="U5" t="n">
-        <v>0.03312562814070349</v>
+        <v>0.03280402010050248</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -31407,49 +31407,49 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2215471698113208</v>
+        <v>0.2193962264150943</v>
       </c>
       <c r="H6" t="n">
-        <v>2.139679245283019</v>
+        <v>2.118905660377359</v>
       </c>
       <c r="I6" t="n">
-        <v>7.627830188679247</v>
+        <v>7.553773584905661</v>
       </c>
       <c r="J6" t="n">
-        <v>20.93134905660378</v>
+        <v>20.7281320754717</v>
       </c>
       <c r="K6" t="n">
-        <v>35.77500943396227</v>
+        <v>35.42767924528302</v>
       </c>
       <c r="L6" t="n">
-        <v>48.10391509433963</v>
+        <v>47.63688679245283</v>
       </c>
       <c r="M6" t="n">
-        <v>56.13499999999999</v>
+        <v>55.58999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>57.62072641509435</v>
+        <v>57.06130188679246</v>
       </c>
       <c r="O6" t="n">
-        <v>52.71170754716981</v>
+        <v>52.19994339622642</v>
       </c>
       <c r="P6" t="n">
-        <v>42.3057924528302</v>
+        <v>41.89505660377359</v>
       </c>
       <c r="Q6" t="n">
-        <v>28.28030188679246</v>
+        <v>28.00573584905661</v>
       </c>
       <c r="R6" t="n">
-        <v>13.75535849056604</v>
+        <v>13.62181132075472</v>
       </c>
       <c r="S6" t="n">
-        <v>4.115141509433959</v>
+        <v>4.07518867924528</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8929905660377355</v>
+        <v>0.8843207547169808</v>
       </c>
       <c r="U6" t="n">
-        <v>0.01457547169811321</v>
+        <v>0.01443396226415095</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -31486,49 +31486,49 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1857377049180328</v>
+        <v>0.1839344262295082</v>
       </c>
       <c r="H7" t="n">
-        <v>1.651377049180329</v>
+        <v>1.635344262295083</v>
       </c>
       <c r="I7" t="n">
-        <v>5.585639344262296</v>
+        <v>5.531409836065575</v>
       </c>
       <c r="J7" t="n">
-        <v>13.13165573770492</v>
+        <v>13.00416393442623</v>
       </c>
       <c r="K7" t="n">
-        <v>21.57934426229507</v>
+        <v>21.36983606557376</v>
       </c>
       <c r="L7" t="n">
-        <v>27.61413114754098</v>
+        <v>27.34603278688525</v>
       </c>
       <c r="M7" t="n">
-        <v>29.11522950819672</v>
+        <v>28.83255737704917</v>
       </c>
       <c r="N7" t="n">
-        <v>28.42293442622952</v>
+        <v>28.1469836065574</v>
       </c>
       <c r="O7" t="n">
-        <v>26.25318032786886</v>
+        <v>25.99829508196722</v>
       </c>
       <c r="P7" t="n">
-        <v>22.46413114754097</v>
+        <v>22.24603278688523</v>
       </c>
       <c r="Q7" t="n">
-        <v>15.553</v>
+        <v>15.402</v>
       </c>
       <c r="R7" t="n">
-        <v>8.351442622950817</v>
+        <v>8.270360655737703</v>
       </c>
       <c r="S7" t="n">
-        <v>3.236901639344261</v>
+        <v>3.205475409836064</v>
       </c>
       <c r="T7" t="n">
-        <v>0.7936065573770489</v>
+        <v>0.785901639344262</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01013114754098362</v>
+        <v>0.01003278688524591</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -31565,49 +31565,49 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4140703517587936</v>
+        <v>0.4100502512562811</v>
       </c>
       <c r="H8" t="n">
-        <v>4.240597989949746</v>
+        <v>4.199427135678389</v>
       </c>
       <c r="I8" t="n">
-        <v>15.96344723618091</v>
+        <v>15.80846231155779</v>
       </c>
       <c r="J8" t="n">
-        <v>35.14370351758794</v>
+        <v>34.80250251256282</v>
       </c>
       <c r="K8" t="n">
-        <v>52.67130150753769</v>
+        <v>52.15992964824121</v>
       </c>
       <c r="L8" t="n">
-        <v>65.34340703517589</v>
+        <v>64.70900502512563</v>
       </c>
       <c r="M8" t="n">
-        <v>72.70713065326633</v>
+        <v>72.00123618090453</v>
       </c>
       <c r="N8" t="n">
-        <v>73.88360804020101</v>
+        <v>73.16629145728643</v>
       </c>
       <c r="O8" t="n">
-        <v>69.76619597989949</v>
+        <v>69.08885427135678</v>
       </c>
       <c r="P8" t="n">
-        <v>59.54383417085427</v>
+        <v>58.96573869346734</v>
       </c>
       <c r="Q8" t="n">
-        <v>44.71493969849246</v>
+        <v>44.28081407035176</v>
       </c>
       <c r="R8" t="n">
-        <v>26.01034673366835</v>
+        <v>25.75781909547739</v>
       </c>
       <c r="S8" t="n">
-        <v>9.435628140703519</v>
+        <v>9.344020100502515</v>
       </c>
       <c r="T8" t="n">
-        <v>1.81259296482412</v>
+        <v>1.794994974874371</v>
       </c>
       <c r="U8" t="n">
-        <v>0.03312562814070349</v>
+        <v>0.03280402010050248</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -31644,49 +31644,49 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2215471698113208</v>
+        <v>0.2193962264150943</v>
       </c>
       <c r="H9" t="n">
-        <v>2.139679245283019</v>
+        <v>2.118905660377359</v>
       </c>
       <c r="I9" t="n">
-        <v>7.627830188679247</v>
+        <v>7.553773584905661</v>
       </c>
       <c r="J9" t="n">
-        <v>20.93134905660378</v>
+        <v>20.7281320754717</v>
       </c>
       <c r="K9" t="n">
-        <v>35.77500943396227</v>
+        <v>35.42767924528302</v>
       </c>
       <c r="L9" t="n">
-        <v>48.10391509433963</v>
+        <v>47.63688679245283</v>
       </c>
       <c r="M9" t="n">
-        <v>56.13499999999999</v>
+        <v>55.58999999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>57.62072641509435</v>
+        <v>57.06130188679246</v>
       </c>
       <c r="O9" t="n">
-        <v>52.71170754716981</v>
+        <v>52.19994339622642</v>
       </c>
       <c r="P9" t="n">
-        <v>42.3057924528302</v>
+        <v>41.89505660377359</v>
       </c>
       <c r="Q9" t="n">
-        <v>28.28030188679246</v>
+        <v>28.00573584905661</v>
       </c>
       <c r="R9" t="n">
-        <v>13.75535849056604</v>
+        <v>13.62181132075472</v>
       </c>
       <c r="S9" t="n">
-        <v>4.115141509433959</v>
+        <v>4.07518867924528</v>
       </c>
       <c r="T9" t="n">
-        <v>0.8929905660377355</v>
+        <v>0.8843207547169808</v>
       </c>
       <c r="U9" t="n">
-        <v>0.01457547169811321</v>
+        <v>0.01443396226415095</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -31723,49 +31723,49 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1857377049180328</v>
+        <v>0.1839344262295082</v>
       </c>
       <c r="H10" t="n">
-        <v>1.651377049180329</v>
+        <v>1.635344262295083</v>
       </c>
       <c r="I10" t="n">
-        <v>5.585639344262296</v>
+        <v>5.531409836065575</v>
       </c>
       <c r="J10" t="n">
-        <v>13.13165573770492</v>
+        <v>13.00416393442623</v>
       </c>
       <c r="K10" t="n">
-        <v>21.57934426229507</v>
+        <v>21.36983606557376</v>
       </c>
       <c r="L10" t="n">
-        <v>27.61413114754098</v>
+        <v>27.34603278688525</v>
       </c>
       <c r="M10" t="n">
-        <v>29.11522950819672</v>
+        <v>28.83255737704917</v>
       </c>
       <c r="N10" t="n">
-        <v>28.42293442622952</v>
+        <v>28.1469836065574</v>
       </c>
       <c r="O10" t="n">
-        <v>26.25318032786886</v>
+        <v>25.99829508196722</v>
       </c>
       <c r="P10" t="n">
-        <v>22.46413114754097</v>
+        <v>22.24603278688523</v>
       </c>
       <c r="Q10" t="n">
-        <v>15.553</v>
+        <v>15.402</v>
       </c>
       <c r="R10" t="n">
-        <v>8.351442622950817</v>
+        <v>8.270360655737703</v>
       </c>
       <c r="S10" t="n">
-        <v>3.236901639344261</v>
+        <v>3.205475409836064</v>
       </c>
       <c r="T10" t="n">
-        <v>0.7936065573770489</v>
+        <v>0.785901639344262</v>
       </c>
       <c r="U10" t="n">
-        <v>0.01013114754098362</v>
+        <v>0.01003278688524591</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -34743,28 +34743,28 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1006972724976123</v>
+        <v>374</v>
       </c>
       <c r="K2" t="n">
-        <v>52.67130150753769</v>
+        <v>373.9999999999999</v>
       </c>
       <c r="L2" t="n">
-        <v>65.3434070351759</v>
+        <v>300.2102102361032</v>
       </c>
       <c r="M2" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="N2" t="n">
-        <v>373</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>180.5571129839088</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>59.25677413017286</v>
+        <v>58.67867865278593</v>
       </c>
       <c r="Q2" t="n">
-        <v>373</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -34822,25 +34822,25 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>142.3822933058598</v>
+        <v>145.9367383131474</v>
       </c>
       <c r="K3" t="n">
-        <v>226.8788640747536</v>
+        <v>226.5315338860743</v>
       </c>
       <c r="L3" t="n">
-        <v>322.1952904430266</v>
+        <v>321.7282621411399</v>
       </c>
       <c r="M3" t="n">
-        <v>143.0850421645043</v>
+        <v>142.5400421645043</v>
       </c>
       <c r="N3" t="n">
-        <v>192.2472765237492</v>
+        <v>191.6878519954473</v>
       </c>
       <c r="O3" t="n">
-        <v>294.1687294499162</v>
+        <v>293.6569652989728</v>
       </c>
       <c r="P3" t="n">
-        <v>155.9717969674834</v>
+        <v>155.5610611184268</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -34880,31 +34880,31 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>61.98558534527646</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>119.0190951630435</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>172.8642181606765</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>228.8979542159473</v>
       </c>
       <c r="J4" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>132.8490622644307</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -34928,25 +34928,25 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>40.83199570698065</v>
       </c>
       <c r="T4" t="n">
-        <v>190.7690400511193</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>249.0517398730831</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>200.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>152.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>29.40547587354363</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -34980,28 +34980,28 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1006972724976123</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>52.67130150753769</v>
+        <v>374</v>
       </c>
       <c r="L5" t="n">
-        <v>65.3434070351759</v>
+        <v>373.9999999999999</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>240.7734830736777</v>
+        <v>374</v>
       </c>
       <c r="O5" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>374</v>
+        <v>58.67867865278593</v>
       </c>
       <c r="Q5" t="n">
-        <v>374</v>
+        <v>300.2102102361032</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -35059,25 +35059,25 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>146.1399552942795</v>
+        <v>145.9367383131474</v>
       </c>
       <c r="K6" t="n">
-        <v>226.8788640747536</v>
+        <v>226.5315338860743</v>
       </c>
       <c r="L6" t="n">
-        <v>322.1952904430266</v>
+        <v>321.7282621411399</v>
       </c>
       <c r="M6" t="n">
-        <v>143.0850421645043</v>
+        <v>142.5400421645043</v>
       </c>
       <c r="N6" t="n">
-        <v>192.2472765237492</v>
+        <v>191.6878519954473</v>
       </c>
       <c r="O6" t="n">
-        <v>294.1687294499162</v>
+        <v>293.6569652989728</v>
       </c>
       <c r="P6" t="n">
-        <v>155.9717969674834</v>
+        <v>155.5610611184268</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -35132,10 +35132,10 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>95.66381988088312</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>228.952183724144</v>
+        <v>228.8979542159473</v>
       </c>
       <c r="J7" t="n">
         <v>374</v>
@@ -35165,13 +35165,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>40.83199570698065</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>56.17540020244445</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -35217,28 +35217,28 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1006972724976123</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>374</v>
       </c>
       <c r="L8" t="n">
+        <v>373.9999999999999</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>300.2102102361031</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>58.67867865278593</v>
+      </c>
+      <c r="Q8" t="n">
         <v>374</v>
-      </c>
-      <c r="M8" t="n">
-        <v>299.5314174862184</v>
-      </c>
-      <c r="N8" t="n">
-        <v>374</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>59.25677413017286</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -35296,25 +35296,25 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>146.1399552942795</v>
+        <v>145.9367383131474</v>
       </c>
       <c r="K9" t="n">
-        <v>226.8788640747536</v>
+        <v>226.5315338860743</v>
       </c>
       <c r="L9" t="n">
-        <v>322.1952904430266</v>
+        <v>321.7282621411399</v>
       </c>
       <c r="M9" t="n">
-        <v>143.0850421645043</v>
+        <v>142.5400421645043</v>
       </c>
       <c r="N9" t="n">
-        <v>192.2472765237492</v>
+        <v>191.6878519954473</v>
       </c>
       <c r="O9" t="n">
-        <v>294.1687294499162</v>
+        <v>293.6569652989728</v>
       </c>
       <c r="P9" t="n">
-        <v>155.9717969674834</v>
+        <v>155.5610611184268</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -35351,37 +35351,37 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>127.2747533519553</v>
       </c>
       <c r="D10" t="n">
-        <v>15.6404561949144</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E10" t="n">
-        <v>119.0190951630435</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>155.141864863388</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>172.8802509475617</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>228.952183724144</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>133.058570461152</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>4.06650298976183</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -35402,25 +35402,25 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>40.86342193648881</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>127.3045786958048</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>249.0516415124273</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>200.8296897837838</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>173.6271901612903</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="11">
@@ -35457,10 +35457,10 @@
         <v>512.6348760697097</v>
       </c>
       <c r="K11" t="n">
-        <v>175.9119195979899</v>
+        <v>648.9999999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>218.2342914572864</v>
+        <v>596.3852235434674</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -35469,13 +35469,13 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>421.6280856303014</v>
+        <v>162.757678164601</v>
       </c>
       <c r="P11" t="n">
         <v>649</v>
       </c>
       <c r="Q11" t="n">
-        <v>592.3686050224903</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -35697,19 +35697,19 @@
         <v>175.9119195979899</v>
       </c>
       <c r="L14" t="n">
-        <v>278.5269147425627</v>
+        <v>477.1046989229868</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>649</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>162.757678164601</v>
       </c>
       <c r="P14" t="n">
-        <v>198.5777841804241</v>
+        <v>649</v>
       </c>
       <c r="Q14" t="n">
         <v>592.3686050224903</v>
@@ -35928,19 +35928,19 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>512.6348760697097</v>
+        <v>82.3301394835529</v>
       </c>
       <c r="K17" t="n">
-        <v>236.2045428832662</v>
+        <v>649</v>
       </c>
       <c r="L17" t="n">
-        <v>218.2342914572864</v>
+        <v>649</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>649</v>
       </c>
       <c r="N17" t="n">
-        <v>649</v>
+        <v>179.1121759491994</v>
       </c>
       <c r="O17" t="n">
         <v>162.757678164601</v>
@@ -35949,7 +35949,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q17" t="n">
-        <v>592.3686050224903</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -36168,7 +36168,7 @@
         <v>82.3301394835529</v>
       </c>
       <c r="K20" t="n">
-        <v>179.1121759491997</v>
+        <v>649</v>
       </c>
       <c r="L20" t="n">
         <v>649</v>
@@ -36177,7 +36177,7 @@
         <v>649</v>
       </c>
       <c r="N20" t="n">
-        <v>649</v>
+        <v>179.1121759491994</v>
       </c>
       <c r="O20" t="n">
         <v>162.757678164601</v>
@@ -36405,25 +36405,25 @@
         <v>82.3301394835529</v>
       </c>
       <c r="K23" t="n">
-        <v>175.9119195979899</v>
+        <v>235.7435709267094</v>
       </c>
       <c r="L23" t="n">
-        <v>218.2342914572864</v>
+        <v>649</v>
       </c>
       <c r="M23" t="n">
-        <v>632.5437490743476</v>
+        <v>649</v>
       </c>
       <c r="N23" t="n">
-        <v>649</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>162.757678164601</v>
       </c>
       <c r="P23" t="n">
-        <v>649</v>
+        <v>198.5777841804241</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>592.3686050224903</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -36639,19 +36639,19 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>82.3301394835529</v>
+        <v>512.6348760697097</v>
       </c>
       <c r="K26" t="n">
-        <v>649</v>
+        <v>648.9999999999999</v>
       </c>
       <c r="L26" t="n">
         <v>649</v>
       </c>
       <c r="M26" t="n">
-        <v>179.1121759491996</v>
+        <v>397.807439363043</v>
       </c>
       <c r="N26" t="n">
-        <v>649</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>162.757678164601</v>
@@ -36791,7 +36791,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H28" t="n">
-        <v>97.74415258690598</v>
+        <v>97.74415258690597</v>
       </c>
       <c r="I28" t="n">
         <v>163.0214951995539</v>
@@ -36876,10 +36876,10 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>512.6348760697097</v>
+        <v>82.3301394835529</v>
       </c>
       <c r="K29" t="n">
-        <v>179.5731479057565</v>
+        <v>175.9119195979899</v>
       </c>
       <c r="L29" t="n">
         <v>218.2342914572864</v>
@@ -36888,7 +36888,7 @@
         <v>649</v>
       </c>
       <c r="N29" t="n">
-        <v>649</v>
+        <v>490.5973598714331</v>
       </c>
       <c r="O29" t="n">
         <v>162.757678164601</v>
@@ -36897,7 +36897,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>592.3686050224903</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -37028,7 +37028,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H31" t="n">
-        <v>97.74415258690597</v>
+        <v>97.74415258690598</v>
       </c>
       <c r="I31" t="n">
         <v>163.0214951995539</v>
@@ -37113,16 +37113,16 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>82.3301394835529</v>
+        <v>512.6348760697097</v>
       </c>
       <c r="K32" t="n">
+        <v>175.9119195979899</v>
+      </c>
+      <c r="L32" t="n">
+        <v>218.2342914572864</v>
+      </c>
+      <c r="M32" t="n">
         <v>649</v>
-      </c>
-      <c r="L32" t="n">
-        <v>649</v>
-      </c>
-      <c r="M32" t="n">
-        <v>179.1121759491996</v>
       </c>
       <c r="N32" t="n">
         <v>649</v>
@@ -37134,7 +37134,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.661228307766413</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -37350,13 +37350,13 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>82.3301394835529</v>
+        <v>512.6348760697097</v>
       </c>
       <c r="K35" t="n">
-        <v>649</v>
+        <v>175.9119195979899</v>
       </c>
       <c r="L35" t="n">
-        <v>235.7435709267094</v>
+        <v>278.5269147425627</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
@@ -37493,7 +37493,7 @@
         <v>35.46378194444452</v>
       </c>
       <c r="E37" t="n">
-        <v>40.01909516304346</v>
+        <v>40.01909516307445</v>
       </c>
       <c r="F37" t="n">
         <v>46.61714403225807</v>
@@ -37502,7 +37502,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H37" t="n">
-        <v>97.74415258690598</v>
+        <v>97.74415258690597</v>
       </c>
       <c r="I37" t="n">
         <v>163.0214951995539</v>
@@ -37590,16 +37590,16 @@
         <v>82.3301394835529</v>
       </c>
       <c r="K38" t="n">
-        <v>649</v>
+        <v>235.7435709267094</v>
       </c>
       <c r="L38" t="n">
         <v>649</v>
       </c>
       <c r="M38" t="n">
-        <v>235.7435709267093</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>649</v>
       </c>
       <c r="O38" t="n">
         <v>162.757678164601</v>
@@ -37727,7 +37727,7 @@
         <v>48.27475335195533</v>
       </c>
       <c r="D40" t="n">
-        <v>35.46378194444451</v>
+        <v>35.46378194444452</v>
       </c>
       <c r="E40" t="n">
         <v>40.01909516304346</v>
@@ -37739,10 +37739,10 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H40" t="n">
-        <v>97.74415258690597</v>
+        <v>97.74415258690598</v>
       </c>
       <c r="I40" t="n">
-        <v>163.0214951995539</v>
+        <v>163.0214951995921</v>
       </c>
       <c r="J40" t="n">
         <v>329.5882314919611</v>
@@ -37824,10 +37824,10 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>512.6348760697097</v>
+        <v>82.3301394835529</v>
       </c>
       <c r="K41" t="n">
-        <v>378.1509320861809</v>
+        <v>175.9119195979899</v>
       </c>
       <c r="L41" t="n">
         <v>218.2342914572864</v>
@@ -37836,16 +37836,16 @@
         <v>649</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>490.5973598714331</v>
       </c>
       <c r="O41" t="n">
         <v>162.757678164601</v>
       </c>
       <c r="P41" t="n">
-        <v>649</v>
+        <v>198.5777841804241</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>592.3686050224903</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -37964,7 +37964,7 @@
         <v>48.27475335195533</v>
       </c>
       <c r="D43" t="n">
-        <v>35.46378194444451</v>
+        <v>35.46378194444452</v>
       </c>
       <c r="E43" t="n">
         <v>40.01909516304346</v>
@@ -38061,19 +38061,19 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>512.6348760697097</v>
+        <v>82.3301394835529</v>
       </c>
       <c r="K44" t="n">
-        <v>648.9999999999999</v>
+        <v>649</v>
       </c>
       <c r="L44" t="n">
         <v>649</v>
       </c>
       <c r="M44" t="n">
-        <v>397.807439363043</v>
+        <v>649</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>179.1121759491994</v>
       </c>
       <c r="O44" t="n">
         <v>162.757678164601</v>
@@ -38213,7 +38213,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H46" t="n">
-        <v>97.74415258690598</v>
+        <v>97.74415258690597</v>
       </c>
       <c r="I46" t="n">
         <v>163.0214951995539</v>
